--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/matrix_scores.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/matrix_scores.xlsx
@@ -14,30 +14,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="6">
   <si>
-    <t>MIX_55</t>
+    <t>PPO_10</t>
   </si>
   <si>
-    <t>MIX_54</t>
+    <t>PPO_13</t>
   </si>
   <si>
-    <t>MIX_44</t>
+    <t>PPO_16</t>
   </si>
   <si>
-    <t>MIX_34</t>
+    <t>PPO_14</t>
   </si>
   <si>
-    <t>MIX_57a</t>
-  </si>
-  <si>
-    <t>MIX_42b</t>
-  </si>
-  <si>
-    <t>MIX_45b</t>
-  </si>
-  <si>
-    <t>MIX_58</t>
+    <t>PPO_401a</t>
   </si>
   <si>
     <t>model</t>
@@ -398,12 +389,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -420,17 +411,8 @@
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -438,227 +420,95 @@
         <v>0.5</v>
       </c>
       <c r="C2">
-        <v>0.504</v>
+        <v>0.007</v>
       </c>
       <c r="D2">
-        <v>0.49</v>
+        <v>0.502</v>
       </c>
       <c r="E2">
-        <v>0.492</v>
+        <v>0.499</v>
       </c>
       <c r="F2">
-        <v>0.039</v>
-      </c>
-      <c r="G2">
-        <v>0.46</v>
-      </c>
-      <c r="H2">
-        <v>0.484</v>
-      </c>
-      <c r="I2">
-        <v>0.91</v>
+        <v>0.502</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.496</v>
+        <v>0.993</v>
       </c>
       <c r="C3">
         <v>0.5</v>
       </c>
       <c r="D3">
-        <v>0.077</v>
+        <v>0.012</v>
       </c>
       <c r="E3">
-        <v>0.497</v>
+        <v>0.006</v>
       </c>
       <c r="F3">
-        <v>0.955</v>
-      </c>
-      <c r="G3">
-        <v>0.71</v>
-      </c>
-      <c r="H3">
-        <v>0.722</v>
-      </c>
-      <c r="I3">
-        <v>0.271</v>
+        <v>0.502</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0.51</v>
+        <v>0.498</v>
       </c>
       <c r="C4">
-        <v>0.923</v>
+        <v>0.988</v>
       </c>
       <c r="D4">
         <v>0.5</v>
       </c>
       <c r="E4">
-        <v>0.025</v>
+        <v>0.5</v>
       </c>
       <c r="F4">
-        <v>0.929</v>
-      </c>
-      <c r="G4">
-        <v>0.703</v>
-      </c>
-      <c r="H4">
-        <v>0.491</v>
-      </c>
-      <c r="I4">
-        <v>0.904</v>
+        <v>0.507</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0.508</v>
+        <v>0.501</v>
       </c>
       <c r="C5">
-        <v>0.503</v>
+        <v>0.994</v>
       </c>
       <c r="D5">
-        <v>0.975</v>
+        <v>0.5</v>
       </c>
       <c r="E5">
         <v>0.5</v>
       </c>
       <c r="F5">
-        <v>0.262</v>
-      </c>
-      <c r="G5">
-        <v>0.5</v>
-      </c>
-      <c r="H5">
-        <v>0.477</v>
-      </c>
-      <c r="I5">
-        <v>0.9370000000000001</v>
+        <v>0.51</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0.961</v>
+        <v>0.498</v>
       </c>
       <c r="C6">
-        <v>0.04500000000000004</v>
+        <v>0.498</v>
       </c>
       <c r="D6">
-        <v>0.07099999999999995</v>
+        <v>0.493</v>
       </c>
       <c r="E6">
-        <v>0.738</v>
+        <v>0.49</v>
       </c>
       <c r="F6">
-        <v>0.5</v>
-      </c>
-      <c r="G6">
-        <v>0.047</v>
-      </c>
-      <c r="H6">
-        <v>0.034</v>
-      </c>
-      <c r="I6">
-        <v>0.504</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>0.54</v>
-      </c>
-      <c r="C7">
-        <v>0.29</v>
-      </c>
-      <c r="D7">
-        <v>0.297</v>
-      </c>
-      <c r="E7">
-        <v>0.5</v>
-      </c>
-      <c r="F7">
-        <v>0.953</v>
-      </c>
-      <c r="G7">
-        <v>0.5</v>
-      </c>
-      <c r="H7">
-        <v>0.51</v>
-      </c>
-      <c r="I7">
-        <v>0.061</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>0.516</v>
-      </c>
-      <c r="C8">
-        <v>0.278</v>
-      </c>
-      <c r="D8">
-        <v>0.509</v>
-      </c>
-      <c r="E8">
-        <v>0.523</v>
-      </c>
-      <c r="F8">
-        <v>0.966</v>
-      </c>
-      <c r="G8">
-        <v>0.49</v>
-      </c>
-      <c r="H8">
-        <v>0.5</v>
-      </c>
-      <c r="I8">
-        <v>0.483</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>0.08999999999999997</v>
-      </c>
-      <c r="C9">
-        <v>0.729</v>
-      </c>
-      <c r="D9">
-        <v>0.09599999999999997</v>
-      </c>
-      <c r="E9">
-        <v>0.06299999999999994</v>
-      </c>
-      <c r="F9">
-        <v>0.496</v>
-      </c>
-      <c r="G9">
-        <v>0.9390000000000001</v>
-      </c>
-      <c r="H9">
-        <v>0.517</v>
-      </c>
-      <c r="I9">
         <v>0.5</v>
       </c>
     </row>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/matrix_scores.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/matrix_scores.xlsx
@@ -14,13 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="6">
-  <si>
-    <t>PPO_10</t>
-  </si>
-  <si>
-    <t>PPO_13</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="4">
   <si>
     <t>PPO_16</t>
   </si>
@@ -28,7 +22,7 @@
     <t>PPO_14</t>
   </si>
   <si>
-    <t>PPO_401a</t>
+    <t>PPO_402</t>
   </si>
   <si>
     <t>model</t>
@@ -389,12 +383,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -405,14 +399,8 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -420,95 +408,37 @@
         <v>0.5</v>
       </c>
       <c r="C2">
-        <v>0.007</v>
+        <v>0.5</v>
       </c>
       <c r="D2">
-        <v>0.502</v>
-      </c>
-      <c r="E2">
-        <v>0.499</v>
-      </c>
-      <c r="F2">
-        <v>0.502</v>
+        <v>0.496</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.993</v>
+        <v>0.5</v>
       </c>
       <c r="C3">
         <v>0.5</v>
       </c>
       <c r="D3">
-        <v>0.012</v>
-      </c>
-      <c r="E3">
-        <v>0.006</v>
-      </c>
-      <c r="F3">
         <v>0.502</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B4">
+        <v>0.504</v>
+      </c>
+      <c r="C4">
         <v>0.498</v>
       </c>
-      <c r="C4">
-        <v>0.988</v>
-      </c>
       <c r="D4">
-        <v>0.5</v>
-      </c>
-      <c r="E4">
-        <v>0.5</v>
-      </c>
-      <c r="F4">
-        <v>0.507</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>0.501</v>
-      </c>
-      <c r="C5">
-        <v>0.994</v>
-      </c>
-      <c r="D5">
-        <v>0.5</v>
-      </c>
-      <c r="E5">
-        <v>0.5</v>
-      </c>
-      <c r="F5">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>0.498</v>
-      </c>
-      <c r="C6">
-        <v>0.498</v>
-      </c>
-      <c r="D6">
-        <v>0.493</v>
-      </c>
-      <c r="E6">
-        <v>0.49</v>
-      </c>
-      <c r="F6">
         <v>0.5</v>
       </c>
     </row>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/matrix_scores.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/matrix_scores.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="5">
   <si>
     <t>PPO_16</t>
   </si>
@@ -22,7 +22,10 @@
     <t>PPO_14</t>
   </si>
   <si>
-    <t>PPO_402</t>
+    <t>PPO_403</t>
+  </si>
+  <si>
+    <t>PPO_404</t>
   </si>
   <si>
     <t>model</t>
@@ -383,12 +386,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -399,8 +402,11 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -411,10 +417,13 @@
         <v>0.5</v>
       </c>
       <c r="D2">
-        <v>0.496</v>
+        <v>0.498</v>
+      </c>
+      <c r="E2">
+        <v>0.011</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -425,20 +434,43 @@
         <v>0.5</v>
       </c>
       <c r="D3">
-        <v>0.502</v>
+        <v>0.992</v>
+      </c>
+      <c r="E3">
+        <v>0.023</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0.504</v>
+        <v>0.502</v>
       </c>
       <c r="C4">
-        <v>0.498</v>
+        <v>0.008000000000000007</v>
       </c>
       <c r="D4">
+        <v>0.5</v>
+      </c>
+      <c r="E4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0.989</v>
+      </c>
+      <c r="C5">
+        <v>0.977</v>
+      </c>
+      <c r="D5">
+        <v>0.5</v>
+      </c>
+      <c r="E5">
         <v>0.5</v>
       </c>
     </row>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/matrix_scores.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/matrix_scores.xlsx
@@ -14,18 +14,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="5">
-  <si>
-    <t>PPO_16</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="4">
   <si>
     <t>PPO_14</t>
   </si>
   <si>
-    <t>PPO_403</t>
+    <t>PPO_404</t>
   </si>
   <si>
-    <t>PPO_404</t>
+    <t>PPO_405</t>
   </si>
   <si>
     <t>model</t>
@@ -386,12 +383,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -402,11 +399,8 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -414,63 +408,37 @@
         <v>0.5</v>
       </c>
       <c r="C2">
-        <v>0.5</v>
+        <v>0.012</v>
       </c>
       <c r="D2">
-        <v>0.498</v>
-      </c>
-      <c r="E2">
-        <v>0.011</v>
+        <v>0.988</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.5</v>
+        <v>0.988</v>
       </c>
       <c r="C3">
         <v>0.5</v>
       </c>
       <c r="D3">
-        <v>0.992</v>
-      </c>
-      <c r="E3">
-        <v>0.023</v>
+        <v>0.006</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0.502</v>
+        <v>0.01200000000000001</v>
       </c>
       <c r="C4">
-        <v>0.008000000000000007</v>
+        <v>0.994</v>
       </c>
       <c r="D4">
-        <v>0.5</v>
-      </c>
-      <c r="E4">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>0.989</v>
-      </c>
-      <c r="C5">
-        <v>0.977</v>
-      </c>
-      <c r="D5">
-        <v>0.5</v>
-      </c>
-      <c r="E5">
         <v>0.5</v>
       </c>
     </row>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/matrix_scores.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/matrix_scores.xlsx
@@ -19,10 +19,10 @@
     <t>PPO_14</t>
   </si>
   <si>
-    <t>PPO_404</t>
+    <t>PPO_405</t>
   </si>
   <si>
-    <t>PPO_405</t>
+    <t>PPO_408</t>
   </si>
   <si>
     <t>model</t>
@@ -408,10 +408,10 @@
         <v>0.5</v>
       </c>
       <c r="C2">
-        <v>0.012</v>
+        <v>0.992</v>
       </c>
       <c r="D2">
-        <v>0.988</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -419,13 +419,13 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.988</v>
+        <v>0.008000000000000007</v>
       </c>
       <c r="C3">
         <v>0.5</v>
       </c>
       <c r="D3">
-        <v>0.006</v>
+        <v>0.504</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -433,10 +433,10 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0.01200000000000001</v>
+        <v>0.984</v>
       </c>
       <c r="C4">
-        <v>0.994</v>
+        <v>0.496</v>
       </c>
       <c r="D4">
         <v>0.5</v>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/matrix_scores.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/matrix_scores.xlsx
@@ -16,13 +16,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="4">
   <si>
-    <t>PPO_14</t>
+    <t>PPO_413</t>
   </si>
   <si>
-    <t>PPO_405</t>
+    <t>PPO_507</t>
   </si>
   <si>
-    <t>PPO_408</t>
+    <t>PPO_601</t>
   </si>
   <si>
     <t>model</t>
@@ -408,10 +408,10 @@
         <v>0.5</v>
       </c>
       <c r="C2">
-        <v>0.992</v>
+        <v>0.5</v>
       </c>
       <c r="D2">
-        <v>0.016</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -419,7 +419,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.008000000000000007</v>
+        <v>0.5</v>
       </c>
       <c r="C3">
         <v>0.5</v>
@@ -433,7 +433,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0.984</v>
+        <v>0.994</v>
       </c>
       <c r="C4">
         <v>0.496</v>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/matrix_scores.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/matrix_scores.xlsx
@@ -14,15 +14,45 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="4">
-  <si>
-    <t>PPO_413</t>
-  </si>
-  <si>
-    <t>PPO_507</t>
-  </si>
-  <si>
-    <t>PPO_601</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="14">
+  <si>
+    <t>PPO_817</t>
+  </si>
+  <si>
+    <t>PPO_820</t>
+  </si>
+  <si>
+    <t>PPO_827</t>
+  </si>
+  <si>
+    <t>PPO_832</t>
+  </si>
+  <si>
+    <t>PPO_812</t>
+  </si>
+  <si>
+    <t>PPO_834</t>
+  </si>
+  <si>
+    <t>PPO_836</t>
+  </si>
+  <si>
+    <t>PPO_838</t>
+  </si>
+  <si>
+    <t>PPO_842</t>
+  </si>
+  <si>
+    <t>PPO_845</t>
+  </si>
+  <si>
+    <t>PPO_846</t>
+  </si>
+  <si>
+    <t>PPO_909</t>
+  </si>
+  <si>
+    <t>PPO_914</t>
   </si>
   <si>
     <t>model</t>
@@ -383,12 +413,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -399,8 +429,38 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -408,37 +468,567 @@
         <v>0.5</v>
       </c>
       <c r="C2">
-        <v>0.5</v>
+        <v>0.015</v>
       </c>
       <c r="D2">
-        <v>0.006</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>0.99</v>
+      </c>
+      <c r="E2">
+        <v>0.502</v>
+      </c>
+      <c r="F2">
+        <v>0.5</v>
+      </c>
+      <c r="G2">
+        <v>0.506</v>
+      </c>
+      <c r="H2">
+        <v>0.007</v>
+      </c>
+      <c r="I2">
+        <v>0.499</v>
+      </c>
+      <c r="J2">
+        <v>0.01</v>
+      </c>
+      <c r="K2">
+        <v>0.01</v>
+      </c>
+      <c r="L2">
+        <v>0.014</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.5</v>
+        <v>0.985</v>
       </c>
       <c r="C3">
         <v>0.5</v>
       </c>
       <c r="D3">
-        <v>0.504</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0.498</v>
+      </c>
+      <c r="F3">
+        <v>0.018</v>
+      </c>
+      <c r="G3">
+        <v>0.5</v>
+      </c>
+      <c r="H3">
+        <v>0.004</v>
+      </c>
+      <c r="I3">
+        <v>0.014</v>
+      </c>
+      <c r="J3">
+        <v>0.018</v>
+      </c>
+      <c r="K3">
+        <v>0.022</v>
+      </c>
+      <c r="L3">
+        <v>0.002</v>
+      </c>
+      <c r="M3">
+        <v>0.014</v>
+      </c>
+      <c r="N3">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B4">
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>0.5</v>
+      </c>
+      <c r="E4">
+        <v>0.498</v>
+      </c>
+      <c r="F4">
+        <v>0.008</v>
+      </c>
+      <c r="G4">
+        <v>0.498</v>
+      </c>
+      <c r="H4">
+        <v>0.497</v>
+      </c>
+      <c r="I4">
+        <v>0.498</v>
+      </c>
+      <c r="J4">
+        <v>0.022</v>
+      </c>
+      <c r="K4">
+        <v>0.5</v>
+      </c>
+      <c r="L4">
+        <v>0.496</v>
+      </c>
+      <c r="M4">
+        <v>0.01</v>
+      </c>
+      <c r="N4">
+        <v>0.498</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0.498</v>
+      </c>
+      <c r="C5">
+        <v>0.502</v>
+      </c>
+      <c r="D5">
+        <v>0.502</v>
+      </c>
+      <c r="E5">
+        <v>0.5</v>
+      </c>
+      <c r="F5">
+        <v>0.008</v>
+      </c>
+      <c r="G5">
+        <v>0.014</v>
+      </c>
+      <c r="H5">
+        <v>0.5</v>
+      </c>
+      <c r="I5">
+        <v>0.498</v>
+      </c>
+      <c r="J5">
+        <v>0.494</v>
+      </c>
+      <c r="K5">
+        <v>0.498</v>
+      </c>
+      <c r="L5">
+        <v>0.988</v>
+      </c>
+      <c r="M5">
+        <v>0.492</v>
+      </c>
+      <c r="N5">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0.5</v>
+      </c>
+      <c r="C6">
+        <v>0.982</v>
+      </c>
+      <c r="D6">
+        <v>0.992</v>
+      </c>
+      <c r="E6">
+        <v>0.992</v>
+      </c>
+      <c r="F6">
+        <v>0.5</v>
+      </c>
+      <c r="G6">
+        <v>0.988</v>
+      </c>
+      <c r="H6">
+        <v>0.007</v>
+      </c>
+      <c r="I6">
+        <v>0.499</v>
+      </c>
+      <c r="J6">
+        <v>0.019</v>
+      </c>
+      <c r="K6">
+        <v>0.011</v>
+      </c>
+      <c r="L6">
+        <v>0.502</v>
+      </c>
+      <c r="M6">
+        <v>0.006</v>
+      </c>
+      <c r="N6">
+        <v>0.498</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>0.494</v>
+      </c>
+      <c r="C7">
+        <v>0.5</v>
+      </c>
+      <c r="D7">
+        <v>0.502</v>
+      </c>
+      <c r="E7">
+        <v>0.986</v>
+      </c>
+      <c r="F7">
+        <v>0.01200000000000001</v>
+      </c>
+      <c r="G7">
+        <v>0.5</v>
+      </c>
+      <c r="H7">
+        <v>0.027</v>
+      </c>
+      <c r="I7">
+        <v>0.5</v>
+      </c>
+      <c r="J7">
+        <v>0.01</v>
+      </c>
+      <c r="K7">
+        <v>0.495</v>
+      </c>
+      <c r="L7">
+        <v>0.004</v>
+      </c>
+      <c r="M7">
+        <v>0.012</v>
+      </c>
+      <c r="N7">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>0.993</v>
+      </c>
+      <c r="C8">
+        <v>0.996</v>
+      </c>
+      <c r="D8">
+        <v>0.503</v>
+      </c>
+      <c r="E8">
+        <v>0.5</v>
+      </c>
+      <c r="F8">
+        <v>0.993</v>
+      </c>
+      <c r="G8">
+        <v>0.973</v>
+      </c>
+      <c r="H8">
+        <v>0.5</v>
+      </c>
+      <c r="I8">
+        <v>0.5</v>
+      </c>
+      <c r="J8">
+        <v>0.262</v>
+      </c>
+      <c r="K8">
+        <v>0.255</v>
+      </c>
+      <c r="L8">
+        <v>0.49</v>
+      </c>
+      <c r="M8">
+        <v>0.245</v>
+      </c>
+      <c r="N8">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.501</v>
+      </c>
+      <c r="C9">
+        <v>0.986</v>
+      </c>
+      <c r="D9">
+        <v>0.502</v>
+      </c>
+      <c r="E9">
+        <v>0.502</v>
+      </c>
+      <c r="F9">
+        <v>0.501</v>
+      </c>
+      <c r="G9">
+        <v>0.5</v>
+      </c>
+      <c r="H9">
+        <v>0.5</v>
+      </c>
+      <c r="I9">
+        <v>0.5</v>
+      </c>
+      <c r="J9">
+        <v>0.014</v>
+      </c>
+      <c r="K9">
+        <v>0.5</v>
+      </c>
+      <c r="L9">
+        <v>0.502</v>
+      </c>
+      <c r="M9">
+        <v>0.016</v>
+      </c>
+      <c r="N9">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.99</v>
+      </c>
+      <c r="C10">
+        <v>0.982</v>
+      </c>
+      <c r="D10">
+        <v>0.978</v>
+      </c>
+      <c r="E10">
+        <v>0.506</v>
+      </c>
+      <c r="F10">
+        <v>0.981</v>
+      </c>
+      <c r="G10">
+        <v>0.99</v>
+      </c>
+      <c r="H10">
+        <v>0.738</v>
+      </c>
+      <c r="I10">
+        <v>0.986</v>
+      </c>
+      <c r="J10">
+        <v>0.5</v>
+      </c>
+      <c r="K10">
+        <v>0.747</v>
+      </c>
+      <c r="L10">
+        <v>0.997</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0.99</v>
+      </c>
+      <c r="C11">
+        <v>0.978</v>
+      </c>
+      <c r="D11">
+        <v>0.5</v>
+      </c>
+      <c r="E11">
+        <v>0.502</v>
+      </c>
+      <c r="F11">
+        <v>0.989</v>
+      </c>
+      <c r="G11">
+        <v>0.505</v>
+      </c>
+      <c r="H11">
+        <v>0.745</v>
+      </c>
+      <c r="I11">
+        <v>0.5</v>
+      </c>
+      <c r="J11">
+        <v>0.253</v>
+      </c>
+      <c r="K11">
+        <v>0.5</v>
+      </c>
+      <c r="L11">
+        <v>0.498</v>
+      </c>
+      <c r="M11">
+        <v>0.249</v>
+      </c>
+      <c r="N11">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0.986</v>
+      </c>
+      <c r="C12">
+        <v>0.998</v>
+      </c>
+      <c r="D12">
+        <v>0.504</v>
+      </c>
+      <c r="E12">
+        <v>0.01200000000000001</v>
+      </c>
+      <c r="F12">
+        <v>0.498</v>
+      </c>
+      <c r="G12">
+        <v>0.996</v>
+      </c>
+      <c r="H12">
+        <v>0.51</v>
+      </c>
+      <c r="I12">
+        <v>0.498</v>
+      </c>
+      <c r="J12">
+        <v>0.003000000000000003</v>
+      </c>
+      <c r="K12">
+        <v>0.502</v>
+      </c>
+      <c r="L12">
+        <v>0.5</v>
+      </c>
+      <c r="M12">
+        <v>0.016</v>
+      </c>
+      <c r="N12">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>0.986</v>
+      </c>
+      <c r="D13">
+        <v>0.99</v>
+      </c>
+      <c r="E13">
+        <v>0.508</v>
+      </c>
+      <c r="F13">
         <v>0.994</v>
       </c>
-      <c r="C4">
-        <v>0.496</v>
-      </c>
-      <c r="D4">
+      <c r="G13">
+        <v>0.988</v>
+      </c>
+      <c r="H13">
+        <v>0.755</v>
+      </c>
+      <c r="I13">
+        <v>0.984</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>0.751</v>
+      </c>
+      <c r="L13">
+        <v>0.984</v>
+      </c>
+      <c r="M13">
+        <v>0.5</v>
+      </c>
+      <c r="N13">
+        <v>0.998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>0.995</v>
+      </c>
+      <c r="D14">
+        <v>0.502</v>
+      </c>
+      <c r="E14">
+        <v>0.5</v>
+      </c>
+      <c r="F14">
+        <v>0.502</v>
+      </c>
+      <c r="G14">
+        <v>0.997</v>
+      </c>
+      <c r="H14">
+        <v>0.99</v>
+      </c>
+      <c r="I14">
+        <v>0.99</v>
+      </c>
+      <c r="J14">
+        <v>0.996</v>
+      </c>
+      <c r="K14">
+        <v>0.994</v>
+      </c>
+      <c r="L14">
+        <v>0.994</v>
+      </c>
+      <c r="M14">
+        <v>0.002000000000000002</v>
+      </c>
+      <c r="N14">
         <v>0.5</v>
       </c>
     </row>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/matrix_scores.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/matrix_scores.xlsx
@@ -14,9 +14,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="14">
-  <si>
-    <t>PPO_817</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="17">
+  <si>
+    <t>PPO_849</t>
   </si>
   <si>
     <t>PPO_820</t>
@@ -25,34 +25,43 @@
     <t>PPO_827</t>
   </si>
   <si>
+    <t>PPO_851</t>
+  </si>
+  <si>
+    <t>PPO_812</t>
+  </si>
+  <si>
     <t>PPO_832</t>
   </si>
   <si>
-    <t>PPO_812</t>
-  </si>
-  <si>
-    <t>PPO_834</t>
-  </si>
-  <si>
-    <t>PPO_836</t>
-  </si>
-  <si>
-    <t>PPO_838</t>
-  </si>
-  <si>
     <t>PPO_842</t>
   </si>
   <si>
-    <t>PPO_845</t>
-  </si>
-  <si>
-    <t>PPO_846</t>
+    <t>PPO_850</t>
+  </si>
+  <si>
+    <t>PPO_852X</t>
   </si>
   <si>
     <t>PPO_909</t>
   </si>
   <si>
     <t>PPO_914</t>
+  </si>
+  <si>
+    <t>PPO_915</t>
+  </si>
+  <si>
+    <t>PPO_918</t>
+  </si>
+  <si>
+    <t>PPO_919</t>
+  </si>
+  <si>
+    <t>SOUP_9</t>
+  </si>
+  <si>
+    <t>X_1</t>
   </si>
   <si>
     <t>model</t>
@@ -413,12 +422,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -459,8 +468,17 @@
       <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -468,57 +486,66 @@
         <v>0.5</v>
       </c>
       <c r="C2">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="D2">
-        <v>0.99</v>
+        <v>0.498</v>
       </c>
       <c r="E2">
-        <v>0.502</v>
+        <v>0.992</v>
       </c>
       <c r="F2">
-        <v>0.5</v>
+        <v>0.496</v>
       </c>
       <c r="G2">
-        <v>0.506</v>
+        <v>0.986</v>
       </c>
       <c r="H2">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="I2">
-        <v>0.499</v>
+        <v>0.504</v>
       </c>
       <c r="J2">
-        <v>0.01</v>
+        <v>0.504</v>
       </c>
       <c r="K2">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="L2">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.496</v>
       </c>
       <c r="N2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>0.496</v>
+      </c>
+      <c r="O2">
+        <v>0.992</v>
+      </c>
+      <c r="P2">
+        <v>0.013</v>
+      </c>
+      <c r="Q2">
+        <v>0.504</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.985</v>
+        <v>0.988</v>
       </c>
       <c r="C3">
         <v>0.5</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="E3">
-        <v>0.498</v>
+        <v>0.5</v>
       </c>
       <c r="F3">
         <v>0.018</v>
@@ -527,508 +554,775 @@
         <v>0.5</v>
       </c>
       <c r="H3">
+        <v>0.024</v>
+      </c>
+      <c r="I3">
         <v>0.004</v>
       </c>
-      <c r="I3">
-        <v>0.014</v>
-      </c>
       <c r="J3">
-        <v>0.018</v>
+        <v>0.504</v>
       </c>
       <c r="K3">
-        <v>0.022</v>
+        <v>0.006</v>
       </c>
       <c r="L3">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="M3">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="N3">
-        <v>0.005</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>0.49</v>
+      </c>
+      <c r="O3">
+        <v>0.494</v>
+      </c>
+      <c r="P3">
+        <v>0.004</v>
+      </c>
+      <c r="Q3">
+        <v>0.016</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0.01000000000000001</v>
+        <v>0.502</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0.998</v>
       </c>
       <c r="D4">
         <v>0.5</v>
       </c>
       <c r="E4">
-        <v>0.498</v>
+        <v>0.5</v>
       </c>
       <c r="F4">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="G4">
-        <v>0.498</v>
+        <v>0.5</v>
       </c>
       <c r="H4">
+        <v>0.016</v>
+      </c>
+      <c r="I4">
         <v>0.497</v>
       </c>
-      <c r="I4">
-        <v>0.498</v>
-      </c>
       <c r="J4">
-        <v>0.022</v>
+        <v>0.016</v>
       </c>
       <c r="K4">
-        <v>0.5</v>
+        <v>0.014</v>
       </c>
       <c r="L4">
+        <v>0.494</v>
+      </c>
+      <c r="M4">
+        <v>0.5</v>
+      </c>
+      <c r="N4">
         <v>0.496</v>
       </c>
-      <c r="M4">
-        <v>0.01</v>
-      </c>
-      <c r="N4">
-        <v>0.498</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4">
+        <v>0.496</v>
+      </c>
+      <c r="P4">
+        <v>0.499</v>
+      </c>
+      <c r="Q4">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0.498</v>
+        <v>0.008000000000000007</v>
       </c>
       <c r="C5">
+        <v>0.5</v>
+      </c>
+      <c r="D5">
+        <v>0.5</v>
+      </c>
+      <c r="E5">
+        <v>0.5</v>
+      </c>
+      <c r="F5">
+        <v>0.012</v>
+      </c>
+      <c r="G5">
         <v>0.502</v>
       </c>
-      <c r="D5">
-        <v>0.502</v>
-      </c>
-      <c r="E5">
-        <v>0.5</v>
-      </c>
-      <c r="F5">
-        <v>0.008</v>
-      </c>
-      <c r="G5">
-        <v>0.014</v>
-      </c>
       <c r="H5">
         <v>0.5</v>
       </c>
       <c r="I5">
-        <v>0.498</v>
+        <v>0.501</v>
       </c>
       <c r="J5">
-        <v>0.494</v>
+        <v>0.988</v>
       </c>
       <c r="K5">
-        <v>0.498</v>
+        <v>0.002</v>
       </c>
       <c r="L5">
-        <v>0.988</v>
+        <v>0.496</v>
       </c>
       <c r="M5">
-        <v>0.492</v>
+        <v>0.003</v>
       </c>
       <c r="N5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>0.006</v>
+      </c>
+      <c r="O5">
+        <v>0.49</v>
+      </c>
+      <c r="P5">
+        <v>0.002</v>
+      </c>
+      <c r="Q5">
+        <v>0.007</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0.5</v>
+        <v>0.504</v>
       </c>
       <c r="C6">
         <v>0.982</v>
       </c>
       <c r="D6">
-        <v>0.992</v>
+        <v>0.994</v>
       </c>
       <c r="E6">
-        <v>0.992</v>
+        <v>0.988</v>
       </c>
       <c r="F6">
         <v>0.5</v>
       </c>
       <c r="G6">
-        <v>0.988</v>
+        <v>0.996</v>
       </c>
       <c r="H6">
-        <v>0.007</v>
+        <v>0.015</v>
       </c>
       <c r="I6">
-        <v>0.499</v>
+        <v>0.021</v>
       </c>
       <c r="J6">
-        <v>0.019</v>
+        <v>0.996</v>
       </c>
       <c r="K6">
-        <v>0.011</v>
+        <v>0.008</v>
       </c>
       <c r="L6">
+        <v>0.498</v>
+      </c>
+      <c r="M6">
+        <v>0.01</v>
+      </c>
+      <c r="N6">
+        <v>0.49</v>
+      </c>
+      <c r="O6">
+        <v>0.5</v>
+      </c>
+      <c r="P6">
+        <v>0.01</v>
+      </c>
+      <c r="Q6">
         <v>0.502</v>
       </c>
-      <c r="M6">
-        <v>0.006</v>
-      </c>
-      <c r="N6">
-        <v>0.498</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B7">
+        <v>0.01400000000000001</v>
+      </c>
+      <c r="C7">
+        <v>0.5</v>
+      </c>
+      <c r="D7">
+        <v>0.5</v>
+      </c>
+      <c r="E7">
+        <v>0.498</v>
+      </c>
+      <c r="F7">
+        <v>0.004000000000000004</v>
+      </c>
+      <c r="G7">
+        <v>0.5</v>
+      </c>
+      <c r="H7">
+        <v>0.493</v>
+      </c>
+      <c r="I7">
+        <v>0.49</v>
+      </c>
+      <c r="J7">
+        <v>0.5</v>
+      </c>
+      <c r="K7">
+        <v>0.496</v>
+      </c>
+      <c r="L7">
+        <v>0.498</v>
+      </c>
+      <c r="M7">
+        <v>0.002</v>
+      </c>
+      <c r="N7">
         <v>0.494</v>
       </c>
-      <c r="C7">
-        <v>0.5</v>
-      </c>
-      <c r="D7">
-        <v>0.502</v>
-      </c>
-      <c r="E7">
-        <v>0.986</v>
-      </c>
-      <c r="F7">
-        <v>0.01200000000000001</v>
-      </c>
-      <c r="G7">
-        <v>0.5</v>
-      </c>
-      <c r="H7">
-        <v>0.027</v>
-      </c>
-      <c r="I7">
-        <v>0.5</v>
-      </c>
-      <c r="J7">
-        <v>0.01</v>
-      </c>
-      <c r="K7">
-        <v>0.495</v>
-      </c>
-      <c r="L7">
-        <v>0.004</v>
-      </c>
-      <c r="M7">
-        <v>0.012</v>
-      </c>
-      <c r="N7">
-        <v>0.003</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7">
+        <v>0.498</v>
+      </c>
+      <c r="P7">
+        <v>0.494</v>
+      </c>
+      <c r="Q7">
+        <v>0.011</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B8">
-        <v>0.993</v>
+        <v>0.994</v>
       </c>
       <c r="C8">
-        <v>0.996</v>
+        <v>0.976</v>
       </c>
       <c r="D8">
-        <v>0.503</v>
+        <v>0.984</v>
       </c>
       <c r="E8">
         <v>0.5</v>
       </c>
       <c r="F8">
-        <v>0.993</v>
+        <v>0.985</v>
       </c>
       <c r="G8">
-        <v>0.973</v>
+        <v>0.507</v>
       </c>
       <c r="H8">
         <v>0.5</v>
       </c>
       <c r="I8">
-        <v>0.5</v>
+        <v>0.739</v>
       </c>
       <c r="J8">
-        <v>0.262</v>
+        <v>0.99</v>
       </c>
       <c r="K8">
-        <v>0.255</v>
+        <v>0.008</v>
       </c>
       <c r="L8">
-        <v>0.49</v>
+        <v>0.016</v>
       </c>
       <c r="M8">
-        <v>0.245</v>
+        <v>0.01</v>
       </c>
       <c r="N8">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>0.494</v>
+      </c>
+      <c r="O8">
+        <v>0.986</v>
+      </c>
+      <c r="P8">
+        <v>0.016</v>
+      </c>
+      <c r="Q8">
+        <v>0.992</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B9">
-        <v>0.501</v>
+        <v>0.496</v>
       </c>
       <c r="C9">
-        <v>0.986</v>
+        <v>0.996</v>
       </c>
       <c r="D9">
-        <v>0.502</v>
+        <v>0.503</v>
       </c>
       <c r="E9">
-        <v>0.502</v>
+        <v>0.499</v>
       </c>
       <c r="F9">
-        <v>0.501</v>
+        <v>0.979</v>
       </c>
       <c r="G9">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="H9">
-        <v>0.5</v>
+        <v>0.261</v>
       </c>
       <c r="I9">
         <v>0.5</v>
       </c>
       <c r="J9">
-        <v>0.014</v>
+        <v>0.744</v>
       </c>
       <c r="K9">
-        <v>0.5</v>
+        <v>0.248</v>
       </c>
       <c r="L9">
-        <v>0.502</v>
+        <v>0.006</v>
       </c>
       <c r="M9">
-        <v>0.016</v>
+        <v>0.25</v>
       </c>
       <c r="N9">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>0.5</v>
+      </c>
+      <c r="O9">
+        <v>0.498</v>
+      </c>
+      <c r="P9">
+        <v>0.25</v>
+      </c>
+      <c r="Q9">
+        <v>0.998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B10">
-        <v>0.99</v>
+        <v>0.496</v>
       </c>
       <c r="C10">
+        <v>0.496</v>
+      </c>
+      <c r="D10">
+        <v>0.984</v>
+      </c>
+      <c r="E10">
+        <v>0.01200000000000001</v>
+      </c>
+      <c r="F10">
+        <v>0.004000000000000004</v>
+      </c>
+      <c r="G10">
+        <v>0.5</v>
+      </c>
+      <c r="H10">
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="I10">
+        <v>0.256</v>
+      </c>
+      <c r="J10">
+        <v>0.5</v>
+      </c>
+      <c r="K10">
+        <v>0.014</v>
+      </c>
+      <c r="L10">
+        <v>0.003</v>
+      </c>
+      <c r="M10">
+        <v>0.008</v>
+      </c>
+      <c r="N10">
+        <v>0.492</v>
+      </c>
+      <c r="O10">
+        <v>0.494</v>
+      </c>
+      <c r="P10">
+        <v>0.005</v>
+      </c>
+      <c r="Q10">
         <v>0.982</v>
       </c>
-      <c r="D10">
-        <v>0.978</v>
-      </c>
-      <c r="E10">
-        <v>0.506</v>
-      </c>
-      <c r="F10">
-        <v>0.981</v>
-      </c>
-      <c r="G10">
-        <v>0.99</v>
-      </c>
-      <c r="H10">
-        <v>0.738</v>
-      </c>
-      <c r="I10">
-        <v>0.986</v>
-      </c>
-      <c r="J10">
-        <v>0.5</v>
-      </c>
-      <c r="K10">
-        <v>0.747</v>
-      </c>
-      <c r="L10">
-        <v>0.997</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0.004</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B11">
-        <v>0.99</v>
+        <v>0.986</v>
       </c>
       <c r="C11">
-        <v>0.978</v>
+        <v>0.994</v>
       </c>
       <c r="D11">
-        <v>0.5</v>
+        <v>0.986</v>
       </c>
       <c r="E11">
-        <v>0.502</v>
+        <v>0.998</v>
       </c>
       <c r="F11">
-        <v>0.989</v>
+        <v>0.992</v>
       </c>
       <c r="G11">
-        <v>0.505</v>
+        <v>0.504</v>
       </c>
       <c r="H11">
-        <v>0.745</v>
+        <v>0.992</v>
       </c>
       <c r="I11">
-        <v>0.5</v>
+        <v>0.752</v>
       </c>
       <c r="J11">
-        <v>0.253</v>
+        <v>0.986</v>
       </c>
       <c r="K11">
         <v>0.5</v>
       </c>
       <c r="L11">
-        <v>0.498</v>
+        <v>0.986</v>
       </c>
       <c r="M11">
-        <v>0.249</v>
+        <v>0.499</v>
       </c>
       <c r="N11">
-        <v>0.006</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>0.004</v>
+      </c>
+      <c r="O11">
+        <v>0.496</v>
+      </c>
+      <c r="P11">
+        <v>0.994</v>
+      </c>
+      <c r="Q11">
+        <v>0.996</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B12">
-        <v>0.986</v>
+        <v>0.988</v>
       </c>
       <c r="C12">
-        <v>0.998</v>
+        <v>0.999</v>
       </c>
       <c r="D12">
+        <v>0.506</v>
+      </c>
+      <c r="E12">
         <v>0.504</v>
       </c>
-      <c r="E12">
-        <v>0.01200000000000001</v>
-      </c>
       <c r="F12">
+        <v>0.502</v>
+      </c>
+      <c r="G12">
+        <v>0.502</v>
+      </c>
+      <c r="H12">
+        <v>0.984</v>
+      </c>
+      <c r="I12">
+        <v>0.994</v>
+      </c>
+      <c r="J12">
+        <v>0.997</v>
+      </c>
+      <c r="K12">
+        <v>0.01400000000000001</v>
+      </c>
+      <c r="L12">
+        <v>0.5</v>
+      </c>
+      <c r="M12">
+        <v>0.011</v>
+      </c>
+      <c r="N12">
         <v>0.498</v>
       </c>
-      <c r="G12">
-        <v>0.996</v>
-      </c>
-      <c r="H12">
-        <v>0.51</v>
-      </c>
-      <c r="I12">
-        <v>0.498</v>
-      </c>
-      <c r="J12">
-        <v>0.003000000000000003</v>
-      </c>
-      <c r="K12">
-        <v>0.502</v>
-      </c>
-      <c r="L12">
-        <v>0.5</v>
-      </c>
-      <c r="M12">
-        <v>0.016</v>
-      </c>
-      <c r="N12">
-        <v>0.006</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12">
+        <v>0.5</v>
+      </c>
+      <c r="P12">
+        <v>0.494</v>
+      </c>
+      <c r="Q12">
+        <v>0.978</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>0.504</v>
       </c>
       <c r="C13">
-        <v>0.986</v>
+        <v>0.995</v>
       </c>
       <c r="D13">
+        <v>0.5</v>
+      </c>
+      <c r="E13">
+        <v>0.997</v>
+      </c>
+      <c r="F13">
         <v>0.99</v>
       </c>
-      <c r="E13">
-        <v>0.508</v>
-      </c>
-      <c r="F13">
+      <c r="G13">
+        <v>0.998</v>
+      </c>
+      <c r="H13">
+        <v>0.99</v>
+      </c>
+      <c r="I13">
+        <v>0.75</v>
+      </c>
+      <c r="J13">
+        <v>0.992</v>
+      </c>
+      <c r="K13">
+        <v>0.501</v>
+      </c>
+      <c r="L13">
+        <v>0.989</v>
+      </c>
+      <c r="M13">
+        <v>0.5</v>
+      </c>
+      <c r="N13">
+        <v>0.502</v>
+      </c>
+      <c r="O13">
+        <v>0.492</v>
+      </c>
+      <c r="P13">
+        <v>0.502</v>
+      </c>
+      <c r="Q13">
         <v>0.994</v>
       </c>
-      <c r="G13">
-        <v>0.988</v>
-      </c>
-      <c r="H13">
-        <v>0.755</v>
-      </c>
-      <c r="I13">
-        <v>0.984</v>
-      </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
-      <c r="K13">
-        <v>0.751</v>
-      </c>
-      <c r="L13">
-        <v>0.984</v>
-      </c>
-      <c r="M13">
-        <v>0.5</v>
-      </c>
-      <c r="N13">
-        <v>0.998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>0.504</v>
       </c>
       <c r="C14">
+        <v>0.51</v>
+      </c>
+      <c r="D14">
+        <v>0.504</v>
+      </c>
+      <c r="E14">
+        <v>0.994</v>
+      </c>
+      <c r="F14">
+        <v>0.51</v>
+      </c>
+      <c r="G14">
+        <v>0.506</v>
+      </c>
+      <c r="H14">
+        <v>0.506</v>
+      </c>
+      <c r="I14">
+        <v>0.5</v>
+      </c>
+      <c r="J14">
+        <v>0.508</v>
+      </c>
+      <c r="K14">
+        <v>0.996</v>
+      </c>
+      <c r="L14">
+        <v>0.502</v>
+      </c>
+      <c r="M14">
+        <v>0.498</v>
+      </c>
+      <c r="N14">
+        <v>0.5</v>
+      </c>
+      <c r="O14">
+        <v>0.024</v>
+      </c>
+      <c r="P14">
+        <v>0.988</v>
+      </c>
+      <c r="Q14">
+        <v>0.507</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>0.008000000000000007</v>
+      </c>
+      <c r="C15">
+        <v>0.506</v>
+      </c>
+      <c r="D15">
+        <v>0.504</v>
+      </c>
+      <c r="E15">
+        <v>0.51</v>
+      </c>
+      <c r="F15">
+        <v>0.5</v>
+      </c>
+      <c r="G15">
+        <v>0.502</v>
+      </c>
+      <c r="H15">
+        <v>0.01400000000000001</v>
+      </c>
+      <c r="I15">
+        <v>0.502</v>
+      </c>
+      <c r="J15">
+        <v>0.506</v>
+      </c>
+      <c r="K15">
+        <v>0.504</v>
+      </c>
+      <c r="L15">
+        <v>0.5</v>
+      </c>
+      <c r="M15">
+        <v>0.508</v>
+      </c>
+      <c r="N15">
+        <v>0.976</v>
+      </c>
+      <c r="O15">
+        <v>0.5</v>
+      </c>
+      <c r="P15">
+        <v>0.5</v>
+      </c>
+      <c r="Q15">
+        <v>0.506</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>0.987</v>
+      </c>
+      <c r="C16">
+        <v>0.996</v>
+      </c>
+      <c r="D16">
+        <v>0.501</v>
+      </c>
+      <c r="E16">
+        <v>0.998</v>
+      </c>
+      <c r="F16">
+        <v>0.99</v>
+      </c>
+      <c r="G16">
+        <v>0.506</v>
+      </c>
+      <c r="H16">
+        <v>0.984</v>
+      </c>
+      <c r="I16">
+        <v>0.75</v>
+      </c>
+      <c r="J16">
         <v>0.995</v>
       </c>
-      <c r="D14">
-        <v>0.502</v>
-      </c>
-      <c r="E14">
-        <v>0.5</v>
-      </c>
-      <c r="F14">
-        <v>0.502</v>
-      </c>
-      <c r="G14">
-        <v>0.997</v>
-      </c>
-      <c r="H14">
-        <v>0.99</v>
-      </c>
-      <c r="I14">
-        <v>0.99</v>
-      </c>
-      <c r="J14">
-        <v>0.996</v>
-      </c>
-      <c r="K14">
-        <v>0.994</v>
-      </c>
-      <c r="L14">
-        <v>0.994</v>
-      </c>
-      <c r="M14">
+      <c r="K16">
+        <v>0.006000000000000005</v>
+      </c>
+      <c r="L16">
+        <v>0.506</v>
+      </c>
+      <c r="M16">
+        <v>0.498</v>
+      </c>
+      <c r="N16">
+        <v>0.01200000000000001</v>
+      </c>
+      <c r="O16">
+        <v>0.5</v>
+      </c>
+      <c r="P16">
+        <v>0.5</v>
+      </c>
+      <c r="Q16">
+        <v>0.988</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>0.496</v>
+      </c>
+      <c r="C17">
+        <v>0.984</v>
+      </c>
+      <c r="D17">
+        <v>0.988</v>
+      </c>
+      <c r="E17">
+        <v>0.993</v>
+      </c>
+      <c r="F17">
+        <v>0.498</v>
+      </c>
+      <c r="G17">
+        <v>0.989</v>
+      </c>
+      <c r="H17">
+        <v>0.008000000000000007</v>
+      </c>
+      <c r="I17">
         <v>0.002000000000000002</v>
       </c>
-      <c r="N14">
+      <c r="J17">
+        <v>0.01800000000000002</v>
+      </c>
+      <c r="K17">
+        <v>0.004000000000000004</v>
+      </c>
+      <c r="L17">
+        <v>0.02200000000000002</v>
+      </c>
+      <c r="M17">
+        <v>0.006000000000000005</v>
+      </c>
+      <c r="N17">
+        <v>0.493</v>
+      </c>
+      <c r="O17">
+        <v>0.494</v>
+      </c>
+      <c r="P17">
+        <v>0.01200000000000001</v>
+      </c>
+      <c r="Q17">
         <v>0.5</v>
       </c>
     </row>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/matrix_scores.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/matrix_scores.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="15">
   <si>
     <t>PPO_849</t>
   </si>
@@ -25,7 +25,7 @@
     <t>PPO_827</t>
   </si>
   <si>
-    <t>PPO_851</t>
+    <t>PPO_853</t>
   </si>
   <si>
     <t>PPO_812</t>
@@ -40,9 +40,6 @@
     <t>PPO_850</t>
   </si>
   <si>
-    <t>PPO_852X</t>
-  </si>
-  <si>
     <t>PPO_909</t>
   </si>
   <si>
@@ -58,10 +55,7 @@
     <t>PPO_919</t>
   </si>
   <si>
-    <t>SOUP_9</t>
-  </si>
-  <si>
-    <t>X_1</t>
+    <t>PPO_920</t>
   </si>
   <si>
     <t>model</t>
@@ -422,12 +416,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -471,14 +465,8 @@
       <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17">
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -492,7 +480,7 @@
         <v>0.498</v>
       </c>
       <c r="E2">
-        <v>0.992</v>
+        <v>0.502</v>
       </c>
       <c r="F2">
         <v>0.496</v>
@@ -507,31 +495,25 @@
         <v>0.504</v>
       </c>
       <c r="J2">
-        <v>0.504</v>
+        <v>0.012</v>
       </c>
       <c r="K2">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="L2">
-        <v>0.012</v>
+        <v>0.501</v>
       </c>
       <c r="M2">
         <v>0.496</v>
       </c>
       <c r="N2">
-        <v>0.496</v>
+        <v>0.994</v>
       </c>
       <c r="O2">
-        <v>0.992</v>
-      </c>
-      <c r="P2">
-        <v>0.013</v>
-      </c>
-      <c r="Q2">
-        <v>0.504</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -542,49 +524,43 @@
         <v>0.5</v>
       </c>
       <c r="D3">
-        <v>0.002</v>
+        <v>0.016</v>
       </c>
       <c r="E3">
-        <v>0.5</v>
+        <v>0.508</v>
       </c>
       <c r="F3">
-        <v>0.018</v>
+        <v>0.004</v>
       </c>
       <c r="G3">
         <v>0.5</v>
       </c>
       <c r="H3">
-        <v>0.024</v>
+        <v>0.022</v>
       </c>
       <c r="I3">
+        <v>0.016</v>
+      </c>
+      <c r="J3">
+        <v>0.01</v>
+      </c>
+      <c r="K3">
         <v>0.004</v>
       </c>
-      <c r="J3">
-        <v>0.504</v>
-      </c>
-      <c r="K3">
-        <v>0.006</v>
-      </c>
       <c r="L3">
-        <v>0.001</v>
+        <v>0.01</v>
       </c>
       <c r="M3">
-        <v>0.005</v>
+        <v>0.492</v>
       </c>
       <c r="N3">
-        <v>0.49</v>
+        <v>0.492</v>
       </c>
       <c r="O3">
-        <v>0.494</v>
-      </c>
-      <c r="P3">
-        <v>0.004</v>
-      </c>
-      <c r="Q3">
-        <v>0.016</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17">
+        <v>0.007</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -592,105 +568,93 @@
         <v>0.502</v>
       </c>
       <c r="C4">
-        <v>0.998</v>
+        <v>0.984</v>
       </c>
       <c r="D4">
         <v>0.5</v>
       </c>
       <c r="E4">
-        <v>0.5</v>
+        <v>0.012</v>
       </c>
       <c r="F4">
-        <v>0.006</v>
+        <v>0.014</v>
       </c>
       <c r="G4">
         <v>0.5</v>
       </c>
       <c r="H4">
-        <v>0.016</v>
+        <v>0.022</v>
       </c>
       <c r="I4">
-        <v>0.497</v>
+        <v>0.5</v>
       </c>
       <c r="J4">
-        <v>0.016</v>
+        <v>0.007</v>
       </c>
       <c r="K4">
-        <v>0.014</v>
+        <v>0.5</v>
       </c>
       <c r="L4">
-        <v>0.494</v>
+        <v>0.502</v>
       </c>
       <c r="M4">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="N4">
-        <v>0.496</v>
+        <v>0.498</v>
       </c>
       <c r="O4">
-        <v>0.496</v>
-      </c>
-      <c r="P4">
         <v>0.499</v>
       </c>
-      <c r="Q4">
-        <v>0.012</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17">
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0.008000000000000007</v>
+        <v>0.498</v>
       </c>
       <c r="C5">
-        <v>0.5</v>
+        <v>0.492</v>
       </c>
       <c r="D5">
-        <v>0.5</v>
+        <v>0.988</v>
       </c>
       <c r="E5">
         <v>0.5</v>
       </c>
       <c r="F5">
+        <v>0.497</v>
+      </c>
+      <c r="G5">
+        <v>0.498</v>
+      </c>
+      <c r="H5">
+        <v>0.498</v>
+      </c>
+      <c r="I5">
+        <v>0.498</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
         <v>0.012</v>
       </c>
-      <c r="G5">
-        <v>0.502</v>
-      </c>
-      <c r="H5">
-        <v>0.5</v>
-      </c>
-      <c r="I5">
-        <v>0.501</v>
-      </c>
-      <c r="J5">
-        <v>0.988</v>
-      </c>
-      <c r="K5">
-        <v>0.002</v>
-      </c>
       <c r="L5">
-        <v>0.496</v>
+        <v>0.004</v>
       </c>
       <c r="M5">
-        <v>0.003</v>
+        <v>0.492</v>
       </c>
       <c r="N5">
-        <v>0.006</v>
+        <v>0.498</v>
       </c>
       <c r="O5">
-        <v>0.49</v>
-      </c>
-      <c r="P5">
-        <v>0.002</v>
-      </c>
-      <c r="Q5">
-        <v>0.007</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -698,52 +662,46 @@
         <v>0.504</v>
       </c>
       <c r="C6">
-        <v>0.982</v>
+        <v>0.996</v>
       </c>
       <c r="D6">
+        <v>0.986</v>
+      </c>
+      <c r="E6">
+        <v>0.503</v>
+      </c>
+      <c r="F6">
+        <v>0.5</v>
+      </c>
+      <c r="G6">
         <v>0.994</v>
       </c>
-      <c r="E6">
-        <v>0.988</v>
-      </c>
-      <c r="F6">
-        <v>0.5</v>
-      </c>
-      <c r="G6">
-        <v>0.996</v>
-      </c>
       <c r="H6">
-        <v>0.015</v>
+        <v>0.004</v>
       </c>
       <c r="I6">
-        <v>0.021</v>
+        <v>0.012</v>
       </c>
       <c r="J6">
-        <v>0.996</v>
+        <v>0.006</v>
       </c>
       <c r="K6">
-        <v>0.008</v>
+        <v>0.498</v>
       </c>
       <c r="L6">
-        <v>0.498</v>
+        <v>0.006</v>
       </c>
       <c r="M6">
-        <v>0.01</v>
+        <v>0.492</v>
       </c>
       <c r="N6">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="O6">
-        <v>0.5</v>
-      </c>
-      <c r="P6">
-        <v>0.01</v>
-      </c>
-      <c r="Q6">
-        <v>0.502</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -757,46 +715,40 @@
         <v>0.5</v>
       </c>
       <c r="E7">
-        <v>0.498</v>
+        <v>0.502</v>
       </c>
       <c r="F7">
-        <v>0.004000000000000004</v>
+        <v>0.006000000000000005</v>
       </c>
       <c r="G7">
         <v>0.5</v>
       </c>
       <c r="H7">
-        <v>0.493</v>
+        <v>0.494</v>
       </c>
       <c r="I7">
+        <v>0.495</v>
+      </c>
+      <c r="J7">
+        <v>0.496</v>
+      </c>
+      <c r="K7">
+        <v>0.492</v>
+      </c>
+      <c r="L7">
+        <v>0.006</v>
+      </c>
+      <c r="M7">
+        <v>0.484</v>
+      </c>
+      <c r="N7">
         <v>0.49</v>
       </c>
-      <c r="J7">
-        <v>0.5</v>
-      </c>
-      <c r="K7">
+      <c r="O7">
         <v>0.496</v>
       </c>
-      <c r="L7">
-        <v>0.498</v>
-      </c>
-      <c r="M7">
-        <v>0.002</v>
-      </c>
-      <c r="N7">
-        <v>0.494</v>
-      </c>
-      <c r="O7">
-        <v>0.498</v>
-      </c>
-      <c r="P7">
-        <v>0.494</v>
-      </c>
-      <c r="Q7">
-        <v>0.011</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17">
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -804,52 +756,46 @@
         <v>0.994</v>
       </c>
       <c r="C8">
-        <v>0.976</v>
+        <v>0.978</v>
       </c>
       <c r="D8">
-        <v>0.984</v>
+        <v>0.978</v>
       </c>
       <c r="E8">
-        <v>0.5</v>
+        <v>0.502</v>
       </c>
       <c r="F8">
-        <v>0.985</v>
+        <v>0.996</v>
       </c>
       <c r="G8">
-        <v>0.507</v>
+        <v>0.506</v>
       </c>
       <c r="H8">
         <v>0.5</v>
       </c>
       <c r="I8">
-        <v>0.739</v>
+        <v>0.743</v>
       </c>
       <c r="J8">
-        <v>0.99</v>
+        <v>0.002</v>
       </c>
       <c r="K8">
+        <v>0.014</v>
+      </c>
+      <c r="L8">
+        <v>0.019</v>
+      </c>
+      <c r="M8">
+        <v>0.502</v>
+      </c>
+      <c r="N8">
+        <v>0.992</v>
+      </c>
+      <c r="O8">
         <v>0.008</v>
       </c>
-      <c r="L8">
-        <v>0.016</v>
-      </c>
-      <c r="M8">
-        <v>0.01</v>
-      </c>
-      <c r="N8">
-        <v>0.494</v>
-      </c>
-      <c r="O8">
-        <v>0.986</v>
-      </c>
-      <c r="P8">
-        <v>0.016</v>
-      </c>
-      <c r="Q8">
-        <v>0.992</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17">
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -857,211 +803,187 @@
         <v>0.496</v>
       </c>
       <c r="C9">
-        <v>0.996</v>
+        <v>0.984</v>
       </c>
       <c r="D9">
-        <v>0.503</v>
+        <v>0.5</v>
       </c>
       <c r="E9">
-        <v>0.499</v>
+        <v>0.502</v>
       </c>
       <c r="F9">
-        <v>0.979</v>
+        <v>0.988</v>
       </c>
       <c r="G9">
-        <v>0.51</v>
+        <v>0.505</v>
       </c>
       <c r="H9">
-        <v>0.261</v>
+        <v>0.257</v>
       </c>
       <c r="I9">
         <v>0.5</v>
       </c>
       <c r="J9">
-        <v>0.744</v>
+        <v>0.249</v>
       </c>
       <c r="K9">
-        <v>0.248</v>
+        <v>0.002</v>
       </c>
       <c r="L9">
-        <v>0.006</v>
+        <v>0.249</v>
       </c>
       <c r="M9">
-        <v>0.25</v>
+        <v>0.49</v>
       </c>
       <c r="N9">
-        <v>0.5</v>
+        <v>0.498</v>
       </c>
       <c r="O9">
-        <v>0.498</v>
-      </c>
-      <c r="P9">
-        <v>0.25</v>
-      </c>
-      <c r="Q9">
-        <v>0.998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17">
+        <v>0.008</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B10">
-        <v>0.496</v>
+        <v>0.988</v>
       </c>
       <c r="C10">
-        <v>0.496</v>
+        <v>0.99</v>
       </c>
       <c r="D10">
-        <v>0.984</v>
+        <v>0.993</v>
       </c>
       <c r="E10">
-        <v>0.01200000000000001</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>0.004000000000000004</v>
+        <v>0.994</v>
       </c>
       <c r="G10">
-        <v>0.5</v>
+        <v>0.504</v>
       </c>
       <c r="H10">
-        <v>0.01000000000000001</v>
+        <v>0.998</v>
       </c>
       <c r="I10">
-        <v>0.256</v>
+        <v>0.751</v>
       </c>
       <c r="J10">
         <v>0.5</v>
       </c>
       <c r="K10">
-        <v>0.014</v>
+        <v>0.994</v>
       </c>
       <c r="L10">
-        <v>0.003</v>
+        <v>0.501</v>
       </c>
       <c r="M10">
-        <v>0.008</v>
+        <v>0.016</v>
       </c>
       <c r="N10">
-        <v>0.492</v>
+        <v>0.505</v>
       </c>
       <c r="O10">
-        <v>0.494</v>
-      </c>
-      <c r="P10">
-        <v>0.005</v>
-      </c>
-      <c r="Q10">
-        <v>0.982</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B11">
+        <v>0.987</v>
+      </c>
+      <c r="C11">
+        <v>0.996</v>
+      </c>
+      <c r="D11">
+        <v>0.5</v>
+      </c>
+      <c r="E11">
+        <v>0.988</v>
+      </c>
+      <c r="F11">
+        <v>0.502</v>
+      </c>
+      <c r="G11">
+        <v>0.508</v>
+      </c>
+      <c r="H11">
         <v>0.986</v>
       </c>
-      <c r="C11">
-        <v>0.994</v>
-      </c>
-      <c r="D11">
-        <v>0.986</v>
-      </c>
-      <c r="E11">
+      <c r="I11">
         <v>0.998</v>
       </c>
-      <c r="F11">
-        <v>0.992</v>
-      </c>
-      <c r="G11">
+      <c r="J11">
+        <v>0.006000000000000005</v>
+      </c>
+      <c r="K11">
+        <v>0.5</v>
+      </c>
+      <c r="L11">
+        <v>0.007</v>
+      </c>
+      <c r="M11">
+        <v>0.492</v>
+      </c>
+      <c r="N11">
         <v>0.504</v>
       </c>
-      <c r="H11">
-        <v>0.992</v>
-      </c>
-      <c r="I11">
-        <v>0.752</v>
-      </c>
-      <c r="J11">
-        <v>0.986</v>
-      </c>
-      <c r="K11">
-        <v>0.5</v>
-      </c>
-      <c r="L11">
-        <v>0.986</v>
-      </c>
-      <c r="M11">
+      <c r="O11">
         <v>0.499</v>
       </c>
-      <c r="N11">
-        <v>0.004</v>
-      </c>
-      <c r="O11">
-        <v>0.496</v>
-      </c>
-      <c r="P11">
-        <v>0.994</v>
-      </c>
-      <c r="Q11">
-        <v>0.996</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17">
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B12">
-        <v>0.988</v>
+        <v>0.499</v>
       </c>
       <c r="C12">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
       <c r="D12">
-        <v>0.506</v>
+        <v>0.498</v>
       </c>
       <c r="E12">
-        <v>0.504</v>
+        <v>0.996</v>
       </c>
       <c r="F12">
-        <v>0.502</v>
+        <v>0.994</v>
       </c>
       <c r="G12">
-        <v>0.502</v>
+        <v>0.994</v>
       </c>
       <c r="H12">
-        <v>0.984</v>
+        <v>0.981</v>
       </c>
       <c r="I12">
-        <v>0.994</v>
+        <v>0.751</v>
       </c>
       <c r="J12">
-        <v>0.997</v>
+        <v>0.499</v>
       </c>
       <c r="K12">
-        <v>0.01400000000000001</v>
+        <v>0.993</v>
       </c>
       <c r="L12">
         <v>0.5</v>
       </c>
       <c r="M12">
-        <v>0.011</v>
+        <v>0.501</v>
       </c>
       <c r="N12">
-        <v>0.498</v>
+        <v>0.495</v>
       </c>
       <c r="O12">
         <v>0.5</v>
       </c>
-      <c r="P12">
-        <v>0.494</v>
-      </c>
-      <c r="Q12">
-        <v>0.978</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17">
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -1069,260 +991,136 @@
         <v>0.504</v>
       </c>
       <c r="C13">
-        <v>0.995</v>
+        <v>0.508</v>
       </c>
       <c r="D13">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="E13">
-        <v>0.997</v>
+        <v>0.508</v>
       </c>
       <c r="F13">
-        <v>0.99</v>
+        <v>0.508</v>
       </c>
       <c r="G13">
-        <v>0.998</v>
+        <v>0.516</v>
       </c>
       <c r="H13">
-        <v>0.99</v>
+        <v>0.498</v>
       </c>
       <c r="I13">
-        <v>0.75</v>
+        <v>0.51</v>
       </c>
       <c r="J13">
-        <v>0.992</v>
+        <v>0.984</v>
       </c>
       <c r="K13">
-        <v>0.501</v>
+        <v>0.508</v>
       </c>
       <c r="L13">
+        <v>0.499</v>
+      </c>
+      <c r="M13">
+        <v>0.5</v>
+      </c>
+      <c r="N13">
+        <v>0.008</v>
+      </c>
+      <c r="O13">
         <v>0.989</v>
       </c>
-      <c r="M13">
-        <v>0.5</v>
-      </c>
-      <c r="N13">
-        <v>0.502</v>
-      </c>
-      <c r="O13">
-        <v>0.492</v>
-      </c>
-      <c r="P13">
-        <v>0.502</v>
-      </c>
-      <c r="Q13">
-        <v>0.994</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17">
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B14">
-        <v>0.504</v>
+        <v>0.006000000000000005</v>
       </c>
       <c r="C14">
+        <v>0.508</v>
+      </c>
+      <c r="D14">
+        <v>0.502</v>
+      </c>
+      <c r="E14">
+        <v>0.502</v>
+      </c>
+      <c r="F14">
+        <v>0.5</v>
+      </c>
+      <c r="G14">
         <v>0.51</v>
       </c>
-      <c r="D14">
-        <v>0.504</v>
-      </c>
-      <c r="E14">
-        <v>0.994</v>
-      </c>
-      <c r="F14">
-        <v>0.51</v>
-      </c>
-      <c r="G14">
-        <v>0.506</v>
-      </c>
       <c r="H14">
-        <v>0.506</v>
+        <v>0.008000000000000007</v>
       </c>
       <c r="I14">
-        <v>0.5</v>
+        <v>0.502</v>
       </c>
       <c r="J14">
-        <v>0.508</v>
+        <v>0.495</v>
       </c>
       <c r="K14">
-        <v>0.996</v>
+        <v>0.496</v>
       </c>
       <c r="L14">
-        <v>0.502</v>
+        <v>0.505</v>
       </c>
       <c r="M14">
-        <v>0.498</v>
+        <v>0.992</v>
       </c>
       <c r="N14">
         <v>0.5</v>
       </c>
       <c r="O14">
-        <v>0.024</v>
-      </c>
-      <c r="P14">
-        <v>0.988</v>
-      </c>
-      <c r="Q14">
-        <v>0.507</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B15">
-        <v>0.008000000000000007</v>
+        <v>0.996</v>
       </c>
       <c r="C15">
-        <v>0.506</v>
+        <v>0.993</v>
       </c>
       <c r="D15">
+        <v>0.501</v>
+      </c>
+      <c r="E15">
+        <v>0.996</v>
+      </c>
+      <c r="F15">
+        <v>0.996</v>
+      </c>
+      <c r="G15">
         <v>0.504</v>
       </c>
-      <c r="E15">
-        <v>0.51</v>
-      </c>
-      <c r="F15">
-        <v>0.5</v>
-      </c>
-      <c r="G15">
-        <v>0.502</v>
-      </c>
       <c r="H15">
-        <v>0.01400000000000001</v>
+        <v>0.992</v>
       </c>
       <c r="I15">
-        <v>0.502</v>
+        <v>0.992</v>
       </c>
       <c r="J15">
-        <v>0.506</v>
+        <v>0.01000000000000001</v>
       </c>
       <c r="K15">
-        <v>0.504</v>
+        <v>0.501</v>
       </c>
       <c r="L15">
         <v>0.5</v>
       </c>
       <c r="M15">
-        <v>0.508</v>
+        <v>0.01100000000000001</v>
       </c>
       <c r="N15">
-        <v>0.976</v>
+        <v>0.5</v>
       </c>
       <c r="O15">
-        <v>0.5</v>
-      </c>
-      <c r="P15">
-        <v>0.5</v>
-      </c>
-      <c r="Q15">
-        <v>0.506</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17">
-      <c r="A16" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16">
-        <v>0.987</v>
-      </c>
-      <c r="C16">
-        <v>0.996</v>
-      </c>
-      <c r="D16">
-        <v>0.501</v>
-      </c>
-      <c r="E16">
-        <v>0.998</v>
-      </c>
-      <c r="F16">
-        <v>0.99</v>
-      </c>
-      <c r="G16">
-        <v>0.506</v>
-      </c>
-      <c r="H16">
-        <v>0.984</v>
-      </c>
-      <c r="I16">
-        <v>0.75</v>
-      </c>
-      <c r="J16">
-        <v>0.995</v>
-      </c>
-      <c r="K16">
-        <v>0.006000000000000005</v>
-      </c>
-      <c r="L16">
-        <v>0.506</v>
-      </c>
-      <c r="M16">
-        <v>0.498</v>
-      </c>
-      <c r="N16">
-        <v>0.01200000000000001</v>
-      </c>
-      <c r="O16">
-        <v>0.5</v>
-      </c>
-      <c r="P16">
-        <v>0.5</v>
-      </c>
-      <c r="Q16">
-        <v>0.988</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17">
-      <c r="A17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17">
-        <v>0.496</v>
-      </c>
-      <c r="C17">
-        <v>0.984</v>
-      </c>
-      <c r="D17">
-        <v>0.988</v>
-      </c>
-      <c r="E17">
-        <v>0.993</v>
-      </c>
-      <c r="F17">
-        <v>0.498</v>
-      </c>
-      <c r="G17">
-        <v>0.989</v>
-      </c>
-      <c r="H17">
-        <v>0.008000000000000007</v>
-      </c>
-      <c r="I17">
-        <v>0.002000000000000002</v>
-      </c>
-      <c r="J17">
-        <v>0.01800000000000002</v>
-      </c>
-      <c r="K17">
-        <v>0.004000000000000004</v>
-      </c>
-      <c r="L17">
-        <v>0.02200000000000002</v>
-      </c>
-      <c r="M17">
-        <v>0.006000000000000005</v>
-      </c>
-      <c r="N17">
-        <v>0.493</v>
-      </c>
-      <c r="O17">
-        <v>0.494</v>
-      </c>
-      <c r="P17">
-        <v>0.01200000000000001</v>
-      </c>
-      <c r="Q17">
         <v>0.5</v>
       </c>
     </row>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/matrix_scores.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/matrix_scores.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="16">
   <si>
     <t>PPO_849</t>
   </si>
@@ -56,6 +56,9 @@
   </si>
   <si>
     <t>PPO_920</t>
+  </si>
+  <si>
+    <t>PPO_921</t>
   </si>
   <si>
     <t>model</t>
@@ -416,12 +419,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -465,8 +468,11 @@
       <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -512,8 +518,11 @@
       <c r="O2">
         <v>0.004</v>
       </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="P2">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -524,43 +533,46 @@
         <v>0.5</v>
       </c>
       <c r="D3">
-        <v>0.016</v>
+        <v>0.02</v>
       </c>
       <c r="E3">
-        <v>0.508</v>
+        <v>0.496</v>
       </c>
       <c r="F3">
+        <v>0.002</v>
+      </c>
+      <c r="G3">
+        <v>0.5</v>
+      </c>
+      <c r="H3">
+        <v>0.018</v>
+      </c>
+      <c r="I3">
+        <v>0.022</v>
+      </c>
+      <c r="J3">
         <v>0.004</v>
       </c>
-      <c r="G3">
-        <v>0.5</v>
-      </c>
-      <c r="H3">
-        <v>0.022</v>
-      </c>
-      <c r="I3">
-        <v>0.016</v>
-      </c>
-      <c r="J3">
-        <v>0.01</v>
-      </c>
       <c r="K3">
-        <v>0.004</v>
+        <v>0.013</v>
       </c>
       <c r="L3">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="M3">
         <v>0.492</v>
       </c>
       <c r="N3">
-        <v>0.492</v>
+        <v>0.496</v>
       </c>
       <c r="O3">
-        <v>0.007</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>0.002</v>
+      </c>
+      <c r="P3">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -568,46 +580,49 @@
         <v>0.502</v>
       </c>
       <c r="C4">
-        <v>0.984</v>
+        <v>0.98</v>
       </c>
       <c r="D4">
         <v>0.5</v>
       </c>
       <c r="E4">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="F4">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="G4">
         <v>0.5</v>
       </c>
       <c r="H4">
-        <v>0.022</v>
+        <v>0.01</v>
       </c>
       <c r="I4">
         <v>0.5</v>
       </c>
       <c r="J4">
-        <v>0.007</v>
+        <v>0.011</v>
       </c>
       <c r="K4">
-        <v>0.5</v>
+        <v>0.494</v>
       </c>
       <c r="L4">
+        <v>0.504</v>
+      </c>
+      <c r="M4">
+        <v>0.494</v>
+      </c>
+      <c r="N4">
+        <v>0.494</v>
+      </c>
+      <c r="O4">
+        <v>0.5</v>
+      </c>
+      <c r="P4">
         <v>0.502</v>
       </c>
-      <c r="M4">
-        <v>0.49</v>
-      </c>
-      <c r="N4">
-        <v>0.498</v>
-      </c>
-      <c r="O4">
-        <v>0.499</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -615,46 +630,49 @@
         <v>0.498</v>
       </c>
       <c r="C5">
-        <v>0.492</v>
+        <v>0.504</v>
       </c>
       <c r="D5">
-        <v>0.988</v>
+        <v>0.987</v>
       </c>
       <c r="E5">
         <v>0.5</v>
       </c>
       <c r="F5">
-        <v>0.497</v>
+        <v>0.498</v>
       </c>
       <c r="G5">
         <v>0.498</v>
       </c>
       <c r="H5">
-        <v>0.498</v>
+        <v>0.501</v>
       </c>
       <c r="I5">
-        <v>0.498</v>
+        <v>0.502</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0.012</v>
+        <v>0.002</v>
       </c>
       <c r="L5">
+        <v>0.002</v>
+      </c>
+      <c r="M5">
+        <v>0.488</v>
+      </c>
+      <c r="N5">
+        <v>0.496</v>
+      </c>
+      <c r="O5">
+        <v>0.006</v>
+      </c>
+      <c r="P5">
         <v>0.004</v>
       </c>
-      <c r="M5">
-        <v>0.492</v>
-      </c>
-      <c r="N5">
-        <v>0.498</v>
-      </c>
-      <c r="O5">
-        <v>0.004</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -662,25 +680,25 @@
         <v>0.504</v>
       </c>
       <c r="C6">
-        <v>0.996</v>
+        <v>0.998</v>
       </c>
       <c r="D6">
-        <v>0.986</v>
+        <v>0.99</v>
       </c>
       <c r="E6">
-        <v>0.503</v>
+        <v>0.502</v>
       </c>
       <c r="F6">
         <v>0.5</v>
       </c>
       <c r="G6">
-        <v>0.994</v>
+        <v>0.992</v>
       </c>
       <c r="H6">
-        <v>0.004</v>
+        <v>0.015</v>
       </c>
       <c r="I6">
-        <v>0.012</v>
+        <v>0.016</v>
       </c>
       <c r="J6">
         <v>0.006</v>
@@ -689,19 +707,22 @@
         <v>0.498</v>
       </c>
       <c r="L6">
+        <v>0.022</v>
+      </c>
+      <c r="M6">
+        <v>0.49</v>
+      </c>
+      <c r="N6">
+        <v>0.5</v>
+      </c>
+      <c r="O6">
         <v>0.006</v>
       </c>
-      <c r="M6">
-        <v>0.492</v>
-      </c>
-      <c r="N6">
-        <v>0.5</v>
-      </c>
-      <c r="O6">
-        <v>0.004</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="P6">
+        <v>0.014</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -718,37 +739,40 @@
         <v>0.502</v>
       </c>
       <c r="F7">
-        <v>0.006000000000000005</v>
+        <v>0.008000000000000007</v>
       </c>
       <c r="G7">
         <v>0.5</v>
       </c>
       <c r="H7">
-        <v>0.494</v>
+        <v>0.49</v>
       </c>
       <c r="I7">
-        <v>0.495</v>
+        <v>0.493</v>
       </c>
       <c r="J7">
         <v>0.496</v>
       </c>
       <c r="K7">
+        <v>0.496</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0.486</v>
+      </c>
+      <c r="N7">
+        <v>0.48</v>
+      </c>
+      <c r="O7">
         <v>0.492</v>
       </c>
-      <c r="L7">
-        <v>0.006</v>
-      </c>
-      <c r="M7">
-        <v>0.484</v>
-      </c>
-      <c r="N7">
-        <v>0.49</v>
-      </c>
-      <c r="O7">
-        <v>0.496</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="P7">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -756,46 +780,49 @@
         <v>0.994</v>
       </c>
       <c r="C8">
-        <v>0.978</v>
+        <v>0.982</v>
       </c>
       <c r="D8">
-        <v>0.978</v>
+        <v>0.99</v>
       </c>
       <c r="E8">
-        <v>0.502</v>
+        <v>0.499</v>
       </c>
       <c r="F8">
-        <v>0.996</v>
+        <v>0.985</v>
       </c>
       <c r="G8">
-        <v>0.506</v>
+        <v>0.51</v>
       </c>
       <c r="H8">
         <v>0.5</v>
       </c>
       <c r="I8">
-        <v>0.743</v>
+        <v>0.744</v>
       </c>
       <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0.004</v>
+      </c>
+      <c r="L8">
         <v>0.002</v>
       </c>
-      <c r="K8">
-        <v>0.014</v>
-      </c>
-      <c r="L8">
-        <v>0.019</v>
-      </c>
       <c r="M8">
-        <v>0.502</v>
+        <v>0.49</v>
       </c>
       <c r="N8">
-        <v>0.992</v>
+        <v>0.988</v>
       </c>
       <c r="O8">
-        <v>0.008</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>0.012</v>
+      </c>
+      <c r="P8">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -803,46 +830,49 @@
         <v>0.496</v>
       </c>
       <c r="C9">
+        <v>0.978</v>
+      </c>
+      <c r="D9">
+        <v>0.5</v>
+      </c>
+      <c r="E9">
+        <v>0.498</v>
+      </c>
+      <c r="F9">
         <v>0.984</v>
       </c>
-      <c r="D9">
-        <v>0.5</v>
-      </c>
-      <c r="E9">
-        <v>0.502</v>
-      </c>
-      <c r="F9">
-        <v>0.988</v>
-      </c>
       <c r="G9">
-        <v>0.505</v>
+        <v>0.507</v>
       </c>
       <c r="H9">
-        <v>0.257</v>
+        <v>0.256</v>
       </c>
       <c r="I9">
         <v>0.5</v>
       </c>
       <c r="J9">
-        <v>0.249</v>
+        <v>0.255</v>
       </c>
       <c r="K9">
-        <v>0.002</v>
+        <v>0.014</v>
       </c>
       <c r="L9">
-        <v>0.249</v>
+        <v>0.248</v>
       </c>
       <c r="M9">
-        <v>0.49</v>
+        <v>0.494</v>
       </c>
       <c r="N9">
+        <v>0.496</v>
+      </c>
+      <c r="O9">
+        <v>0.011</v>
+      </c>
+      <c r="P9">
         <v>0.498</v>
       </c>
-      <c r="O9">
-        <v>0.008</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -850,10 +880,10 @@
         <v>0.988</v>
       </c>
       <c r="C10">
-        <v>0.99</v>
+        <v>0.996</v>
       </c>
       <c r="D10">
-        <v>0.993</v>
+        <v>0.989</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -865,10 +895,10 @@
         <v>0.504</v>
       </c>
       <c r="H10">
-        <v>0.998</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>0.751</v>
+        <v>0.745</v>
       </c>
       <c r="J10">
         <v>0.5</v>
@@ -877,19 +907,22 @@
         <v>0.994</v>
       </c>
       <c r="L10">
-        <v>0.501</v>
+        <v>0.498</v>
       </c>
       <c r="M10">
-        <v>0.016</v>
+        <v>0.012</v>
       </c>
       <c r="N10">
-        <v>0.505</v>
+        <v>0.497</v>
       </c>
       <c r="O10">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>0.994</v>
+      </c>
+      <c r="P10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -897,25 +930,25 @@
         <v>0.987</v>
       </c>
       <c r="C11">
-        <v>0.996</v>
+        <v>0.987</v>
       </c>
       <c r="D11">
-        <v>0.5</v>
+        <v>0.506</v>
       </c>
       <c r="E11">
-        <v>0.988</v>
+        <v>0.998</v>
       </c>
       <c r="F11">
         <v>0.502</v>
       </c>
       <c r="G11">
-        <v>0.508</v>
+        <v>0.504</v>
       </c>
       <c r="H11">
+        <v>0.996</v>
+      </c>
+      <c r="I11">
         <v>0.986</v>
-      </c>
-      <c r="I11">
-        <v>0.998</v>
       </c>
       <c r="J11">
         <v>0.006000000000000005</v>
@@ -927,16 +960,19 @@
         <v>0.007</v>
       </c>
       <c r="M11">
-        <v>0.492</v>
+        <v>0.5</v>
       </c>
       <c r="N11">
-        <v>0.504</v>
+        <v>0.502</v>
       </c>
       <c r="O11">
-        <v>0.499</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>0.5</v>
+      </c>
+      <c r="P11">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -944,28 +980,28 @@
         <v>0.499</v>
       </c>
       <c r="C12">
-        <v>0.99</v>
+        <v>0.992</v>
       </c>
       <c r="D12">
-        <v>0.498</v>
+        <v>0.496</v>
       </c>
       <c r="E12">
-        <v>0.996</v>
+        <v>0.998</v>
       </c>
       <c r="F12">
-        <v>0.994</v>
+        <v>0.978</v>
       </c>
       <c r="G12">
-        <v>0.994</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>0.981</v>
+        <v>0.998</v>
       </c>
       <c r="I12">
-        <v>0.751</v>
+        <v>0.752</v>
       </c>
       <c r="J12">
-        <v>0.499</v>
+        <v>0.502</v>
       </c>
       <c r="K12">
         <v>0.993</v>
@@ -974,16 +1010,19 @@
         <v>0.5</v>
       </c>
       <c r="M12">
+        <v>0.502</v>
+      </c>
+      <c r="N12">
+        <v>0.499</v>
+      </c>
+      <c r="O12">
         <v>0.501</v>
       </c>
-      <c r="N12">
+      <c r="P12">
         <v>0.495</v>
       </c>
-      <c r="O12">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -994,43 +1033,46 @@
         <v>0.508</v>
       </c>
       <c r="D13">
+        <v>0.506</v>
+      </c>
+      <c r="E13">
+        <v>0.512</v>
+      </c>
+      <c r="F13">
         <v>0.51</v>
       </c>
-      <c r="E13">
-        <v>0.508</v>
-      </c>
-      <c r="F13">
-        <v>0.508</v>
-      </c>
       <c r="G13">
-        <v>0.516</v>
+        <v>0.514</v>
       </c>
       <c r="H13">
+        <v>0.51</v>
+      </c>
+      <c r="I13">
+        <v>0.506</v>
+      </c>
+      <c r="J13">
+        <v>0.988</v>
+      </c>
+      <c r="K13">
+        <v>0.5</v>
+      </c>
+      <c r="L13">
         <v>0.498</v>
       </c>
-      <c r="I13">
-        <v>0.51</v>
-      </c>
-      <c r="J13">
+      <c r="M13">
+        <v>0.5</v>
+      </c>
+      <c r="N13">
+        <v>0.013</v>
+      </c>
+      <c r="O13">
         <v>0.984</v>
       </c>
-      <c r="K13">
-        <v>0.508</v>
-      </c>
-      <c r="L13">
-        <v>0.499</v>
-      </c>
-      <c r="M13">
-        <v>0.5</v>
-      </c>
-      <c r="N13">
-        <v>0.008</v>
-      </c>
-      <c r="O13">
-        <v>0.989</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="P13">
+        <v>0.503</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -1038,46 +1080,49 @@
         <v>0.006000000000000005</v>
       </c>
       <c r="C14">
-        <v>0.508</v>
+        <v>0.504</v>
       </c>
       <c r="D14">
-        <v>0.502</v>
+        <v>0.506</v>
       </c>
       <c r="E14">
-        <v>0.502</v>
+        <v>0.504</v>
       </c>
       <c r="F14">
         <v>0.5</v>
       </c>
       <c r="G14">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="H14">
-        <v>0.008000000000000007</v>
+        <v>0.01200000000000001</v>
       </c>
       <c r="I14">
-        <v>0.502</v>
+        <v>0.504</v>
       </c>
       <c r="J14">
-        <v>0.495</v>
+        <v>0.503</v>
       </c>
       <c r="K14">
-        <v>0.496</v>
+        <v>0.498</v>
       </c>
       <c r="L14">
-        <v>0.505</v>
+        <v>0.501</v>
       </c>
       <c r="M14">
-        <v>0.992</v>
+        <v>0.987</v>
       </c>
       <c r="N14">
         <v>0.5</v>
       </c>
       <c r="O14">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>0.501</v>
+      </c>
+      <c r="P14">
+        <v>0.499</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -1085,42 +1130,95 @@
         <v>0.996</v>
       </c>
       <c r="C15">
-        <v>0.993</v>
+        <v>0.998</v>
       </c>
       <c r="D15">
+        <v>0.5</v>
+      </c>
+      <c r="E15">
+        <v>0.994</v>
+      </c>
+      <c r="F15">
+        <v>0.994</v>
+      </c>
+      <c r="G15">
+        <v>0.508</v>
+      </c>
+      <c r="H15">
+        <v>0.988</v>
+      </c>
+      <c r="I15">
+        <v>0.989</v>
+      </c>
+      <c r="J15">
+        <v>0.006000000000000005</v>
+      </c>
+      <c r="K15">
+        <v>0.5</v>
+      </c>
+      <c r="L15">
+        <v>0.499</v>
+      </c>
+      <c r="M15">
+        <v>0.01600000000000001</v>
+      </c>
+      <c r="N15">
+        <v>0.499</v>
+      </c>
+      <c r="O15">
+        <v>0.5</v>
+      </c>
+      <c r="P15">
+        <v>0.502</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>0.985</v>
+      </c>
+      <c r="C16">
+        <v>0.994</v>
+      </c>
+      <c r="D16">
+        <v>0.498</v>
+      </c>
+      <c r="E16">
+        <v>0.996</v>
+      </c>
+      <c r="F16">
+        <v>0.986</v>
+      </c>
+      <c r="G16">
+        <v>0.996</v>
+      </c>
+      <c r="H16">
+        <v>0.99</v>
+      </c>
+      <c r="I16">
+        <v>0.502</v>
+      </c>
+      <c r="J16">
+        <v>0.5</v>
+      </c>
+      <c r="K16">
+        <v>0.985</v>
+      </c>
+      <c r="L16">
+        <v>0.505</v>
+      </c>
+      <c r="M16">
+        <v>0.497</v>
+      </c>
+      <c r="N16">
         <v>0.501</v>
       </c>
-      <c r="E15">
-        <v>0.996</v>
-      </c>
-      <c r="F15">
-        <v>0.996</v>
-      </c>
-      <c r="G15">
-        <v>0.504</v>
-      </c>
-      <c r="H15">
-        <v>0.992</v>
-      </c>
-      <c r="I15">
-        <v>0.992</v>
-      </c>
-      <c r="J15">
-        <v>0.01000000000000001</v>
-      </c>
-      <c r="K15">
-        <v>0.501</v>
-      </c>
-      <c r="L15">
-        <v>0.5</v>
-      </c>
-      <c r="M15">
-        <v>0.01100000000000001</v>
-      </c>
-      <c r="N15">
-        <v>0.5</v>
-      </c>
-      <c r="O15">
+      <c r="O16">
+        <v>0.498</v>
+      </c>
+      <c r="P16">
         <v>0.5</v>
       </c>
     </row>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/matrix_scores.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/matrix_scores.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="15">
   <si>
     <t>PPO_849</t>
   </si>
@@ -47,9 +47,6 @@
   </si>
   <si>
     <t>PPO_915</t>
-  </si>
-  <si>
-    <t>PPO_918</t>
   </si>
   <si>
     <t>PPO_919</t>
@@ -419,12 +416,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -468,11 +465,8 @@
       <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -510,19 +504,16 @@
         <v>0.501</v>
       </c>
       <c r="M2">
-        <v>0.496</v>
+        <v>0.982</v>
       </c>
       <c r="N2">
-        <v>0.994</v>
+        <v>0.002</v>
       </c>
       <c r="O2">
         <v>0.004</v>
       </c>
-      <c r="P2">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -533,46 +524,43 @@
         <v>0.5</v>
       </c>
       <c r="D3">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="E3">
-        <v>0.496</v>
+        <v>0.508</v>
       </c>
       <c r="F3">
+        <v>0.004</v>
+      </c>
+      <c r="G3">
+        <v>0.5</v>
+      </c>
+      <c r="H3">
+        <v>0.022</v>
+      </c>
+      <c r="I3">
+        <v>0.016</v>
+      </c>
+      <c r="J3">
+        <v>0.01</v>
+      </c>
+      <c r="K3">
+        <v>0.004</v>
+      </c>
+      <c r="L3">
+        <v>0.01</v>
+      </c>
+      <c r="M3">
+        <v>0.498</v>
+      </c>
+      <c r="N3">
         <v>0.002</v>
       </c>
-      <c r="G3">
-        <v>0.5</v>
-      </c>
-      <c r="H3">
-        <v>0.018</v>
-      </c>
-      <c r="I3">
-        <v>0.022</v>
-      </c>
-      <c r="J3">
-        <v>0.004</v>
-      </c>
-      <c r="K3">
-        <v>0.013</v>
-      </c>
-      <c r="L3">
-        <v>0.008</v>
-      </c>
-      <c r="M3">
-        <v>0.492</v>
-      </c>
-      <c r="N3">
-        <v>0.496</v>
-      </c>
       <c r="O3">
-        <v>0.002</v>
-      </c>
-      <c r="P3">
-        <v>0.006</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -580,49 +568,46 @@
         <v>0.502</v>
       </c>
       <c r="C4">
-        <v>0.98</v>
+        <v>0.984</v>
       </c>
       <c r="D4">
         <v>0.5</v>
       </c>
       <c r="E4">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="F4">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="G4">
         <v>0.5</v>
       </c>
       <c r="H4">
-        <v>0.01</v>
+        <v>0.022</v>
       </c>
       <c r="I4">
         <v>0.5</v>
       </c>
       <c r="J4">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
       <c r="K4">
-        <v>0.494</v>
+        <v>0.5</v>
       </c>
       <c r="L4">
-        <v>0.504</v>
+        <v>0.502</v>
       </c>
       <c r="M4">
-        <v>0.494</v>
+        <v>0.496</v>
       </c>
       <c r="N4">
-        <v>0.494</v>
+        <v>0.503</v>
       </c>
       <c r="O4">
-        <v>0.5</v>
-      </c>
-      <c r="P4">
-        <v>0.502</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
+        <v>0.496</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -630,49 +615,46 @@
         <v>0.498</v>
       </c>
       <c r="C5">
-        <v>0.504</v>
+        <v>0.492</v>
       </c>
       <c r="D5">
-        <v>0.987</v>
+        <v>0.988</v>
       </c>
       <c r="E5">
         <v>0.5</v>
       </c>
       <c r="F5">
-        <v>0.498</v>
+        <v>0.497</v>
       </c>
       <c r="G5">
         <v>0.498</v>
       </c>
       <c r="H5">
-        <v>0.501</v>
+        <v>0.498</v>
       </c>
       <c r="I5">
-        <v>0.502</v>
+        <v>0.498</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0.002</v>
+        <v>0.012</v>
       </c>
       <c r="L5">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="M5">
-        <v>0.488</v>
+        <v>0.494</v>
       </c>
       <c r="N5">
-        <v>0.496</v>
+        <v>0.004</v>
       </c>
       <c r="O5">
         <v>0.006</v>
       </c>
-      <c r="P5">
-        <v>0.004</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -680,25 +662,25 @@
         <v>0.504</v>
       </c>
       <c r="C6">
-        <v>0.998</v>
+        <v>0.996</v>
       </c>
       <c r="D6">
-        <v>0.99</v>
+        <v>0.986</v>
       </c>
       <c r="E6">
-        <v>0.502</v>
+        <v>0.503</v>
       </c>
       <c r="F6">
         <v>0.5</v>
       </c>
       <c r="G6">
-        <v>0.992</v>
+        <v>0.994</v>
       </c>
       <c r="H6">
-        <v>0.015</v>
+        <v>0.004</v>
       </c>
       <c r="I6">
-        <v>0.016</v>
+        <v>0.012</v>
       </c>
       <c r="J6">
         <v>0.006</v>
@@ -707,22 +689,19 @@
         <v>0.498</v>
       </c>
       <c r="L6">
-        <v>0.022</v>
+        <v>0.006</v>
       </c>
       <c r="M6">
-        <v>0.49</v>
+        <v>0.492</v>
       </c>
       <c r="N6">
-        <v>0.5</v>
+        <v>0.012</v>
       </c>
       <c r="O6">
-        <v>0.006</v>
-      </c>
-      <c r="P6">
-        <v>0.014</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -739,40 +718,37 @@
         <v>0.502</v>
       </c>
       <c r="F7">
-        <v>0.008000000000000007</v>
+        <v>0.006000000000000005</v>
       </c>
       <c r="G7">
         <v>0.5</v>
       </c>
       <c r="H7">
-        <v>0.49</v>
+        <v>0.494</v>
       </c>
       <c r="I7">
-        <v>0.493</v>
+        <v>0.495</v>
       </c>
       <c r="J7">
         <v>0.496</v>
       </c>
       <c r="K7">
-        <v>0.496</v>
+        <v>0.492</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="M7">
-        <v>0.486</v>
+        <v>0.484</v>
       </c>
       <c r="N7">
-        <v>0.48</v>
+        <v>0.494</v>
       </c>
       <c r="O7">
-        <v>0.492</v>
-      </c>
-      <c r="P7">
-        <v>0.004</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -780,49 +756,46 @@
         <v>0.994</v>
       </c>
       <c r="C8">
-        <v>0.982</v>
+        <v>0.978</v>
       </c>
       <c r="D8">
+        <v>0.978</v>
+      </c>
+      <c r="E8">
+        <v>0.502</v>
+      </c>
+      <c r="F8">
+        <v>0.996</v>
+      </c>
+      <c r="G8">
+        <v>0.506</v>
+      </c>
+      <c r="H8">
+        <v>0.5</v>
+      </c>
+      <c r="I8">
+        <v>0.743</v>
+      </c>
+      <c r="J8">
+        <v>0.002</v>
+      </c>
+      <c r="K8">
+        <v>0.014</v>
+      </c>
+      <c r="L8">
+        <v>0.019</v>
+      </c>
+      <c r="M8">
         <v>0.99</v>
       </c>
-      <c r="E8">
-        <v>0.499</v>
-      </c>
-      <c r="F8">
-        <v>0.985</v>
-      </c>
-      <c r="G8">
-        <v>0.51</v>
-      </c>
-      <c r="H8">
-        <v>0.5</v>
-      </c>
-      <c r="I8">
-        <v>0.744</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0.004</v>
-      </c>
-      <c r="L8">
-        <v>0.002</v>
-      </c>
-      <c r="M8">
-        <v>0.49</v>
-      </c>
       <c r="N8">
-        <v>0.988</v>
+        <v>0.006</v>
       </c>
       <c r="O8">
-        <v>0.012</v>
-      </c>
-      <c r="P8">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
+        <v>0.008</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -830,49 +803,46 @@
         <v>0.496</v>
       </c>
       <c r="C9">
-        <v>0.978</v>
+        <v>0.984</v>
       </c>
       <c r="D9">
         <v>0.5</v>
       </c>
       <c r="E9">
-        <v>0.498</v>
+        <v>0.502</v>
       </c>
       <c r="F9">
-        <v>0.984</v>
+        <v>0.988</v>
       </c>
       <c r="G9">
-        <v>0.507</v>
+        <v>0.505</v>
       </c>
       <c r="H9">
-        <v>0.256</v>
+        <v>0.257</v>
       </c>
       <c r="I9">
         <v>0.5</v>
       </c>
       <c r="J9">
-        <v>0.255</v>
+        <v>0.249</v>
       </c>
       <c r="K9">
-        <v>0.014</v>
+        <v>0.002</v>
       </c>
       <c r="L9">
-        <v>0.248</v>
+        <v>0.249</v>
       </c>
       <c r="M9">
-        <v>0.494</v>
+        <v>0.49</v>
       </c>
       <c r="N9">
+        <v>0.004</v>
+      </c>
+      <c r="O9">
         <v>0.496</v>
       </c>
-      <c r="O9">
-        <v>0.011</v>
-      </c>
-      <c r="P9">
-        <v>0.498</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -880,10 +850,10 @@
         <v>0.988</v>
       </c>
       <c r="C10">
-        <v>0.996</v>
+        <v>0.99</v>
       </c>
       <c r="D10">
-        <v>0.989</v>
+        <v>0.993</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -895,10 +865,10 @@
         <v>0.504</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>0.998</v>
       </c>
       <c r="I10">
-        <v>0.745</v>
+        <v>0.751</v>
       </c>
       <c r="J10">
         <v>0.5</v>
@@ -907,22 +877,19 @@
         <v>0.994</v>
       </c>
       <c r="L10">
-        <v>0.498</v>
+        <v>0.501</v>
       </c>
       <c r="M10">
-        <v>0.012</v>
+        <v>0.502</v>
       </c>
       <c r="N10">
-        <v>0.497</v>
+        <v>0.982</v>
       </c>
       <c r="O10">
-        <v>0.994</v>
-      </c>
-      <c r="P10">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
+        <v>0.499</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -930,25 +897,25 @@
         <v>0.987</v>
       </c>
       <c r="C11">
-        <v>0.987</v>
+        <v>0.996</v>
       </c>
       <c r="D11">
-        <v>0.506</v>
+        <v>0.5</v>
       </c>
       <c r="E11">
-        <v>0.998</v>
+        <v>0.988</v>
       </c>
       <c r="F11">
         <v>0.502</v>
       </c>
       <c r="G11">
-        <v>0.504</v>
+        <v>0.508</v>
       </c>
       <c r="H11">
-        <v>0.996</v>
+        <v>0.986</v>
       </c>
       <c r="I11">
-        <v>0.986</v>
+        <v>0.998</v>
       </c>
       <c r="J11">
         <v>0.006000000000000005</v>
@@ -960,19 +927,16 @@
         <v>0.007</v>
       </c>
       <c r="M11">
-        <v>0.5</v>
+        <v>0.496</v>
       </c>
       <c r="N11">
-        <v>0.502</v>
+        <v>0.499</v>
       </c>
       <c r="O11">
-        <v>0.5</v>
-      </c>
-      <c r="P11">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -980,28 +944,28 @@
         <v>0.499</v>
       </c>
       <c r="C12">
-        <v>0.992</v>
+        <v>0.99</v>
       </c>
       <c r="D12">
-        <v>0.496</v>
+        <v>0.498</v>
       </c>
       <c r="E12">
-        <v>0.998</v>
+        <v>0.996</v>
       </c>
       <c r="F12">
-        <v>0.978</v>
+        <v>0.994</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>0.994</v>
       </c>
       <c r="H12">
-        <v>0.998</v>
+        <v>0.981</v>
       </c>
       <c r="I12">
-        <v>0.752</v>
+        <v>0.751</v>
       </c>
       <c r="J12">
-        <v>0.502</v>
+        <v>0.499</v>
       </c>
       <c r="K12">
         <v>0.993</v>
@@ -1010,119 +974,110 @@
         <v>0.5</v>
       </c>
       <c r="M12">
-        <v>0.502</v>
+        <v>0.495</v>
       </c>
       <c r="N12">
-        <v>0.499</v>
+        <v>0.501</v>
       </c>
       <c r="O12">
-        <v>0.501</v>
-      </c>
-      <c r="P12">
         <v>0.495</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:15">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B13">
+        <v>0.01800000000000002</v>
+      </c>
+      <c r="C13">
+        <v>0.502</v>
+      </c>
+      <c r="D13">
         <v>0.504</v>
       </c>
-      <c r="C13">
+      <c r="E13">
+        <v>0.506</v>
+      </c>
+      <c r="F13">
         <v>0.508</v>
       </c>
-      <c r="D13">
-        <v>0.506</v>
-      </c>
-      <c r="E13">
-        <v>0.512</v>
-      </c>
-      <c r="F13">
+      <c r="G13">
+        <v>0.516</v>
+      </c>
+      <c r="H13">
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="I13">
         <v>0.51</v>
       </c>
-      <c r="G13">
-        <v>0.514</v>
-      </c>
-      <c r="H13">
-        <v>0.51</v>
-      </c>
-      <c r="I13">
-        <v>0.506</v>
-      </c>
       <c r="J13">
-        <v>0.988</v>
+        <v>0.498</v>
       </c>
       <c r="K13">
-        <v>0.5</v>
+        <v>0.504</v>
       </c>
       <c r="L13">
-        <v>0.498</v>
+        <v>0.505</v>
       </c>
       <c r="M13">
         <v>0.5</v>
       </c>
       <c r="N13">
-        <v>0.013</v>
+        <v>0.497</v>
       </c>
       <c r="O13">
-        <v>0.984</v>
-      </c>
-      <c r="P13">
-        <v>0.503</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B14">
-        <v>0.006000000000000005</v>
+        <v>0.998</v>
       </c>
       <c r="C14">
-        <v>0.504</v>
+        <v>0.998</v>
       </c>
       <c r="D14">
+        <v>0.497</v>
+      </c>
+      <c r="E14">
+        <v>0.996</v>
+      </c>
+      <c r="F14">
+        <v>0.988</v>
+      </c>
+      <c r="G14">
         <v>0.506</v>
       </c>
-      <c r="E14">
-        <v>0.504</v>
-      </c>
-      <c r="F14">
-        <v>0.5</v>
-      </c>
-      <c r="G14">
-        <v>0.52</v>
-      </c>
       <c r="H14">
-        <v>0.01200000000000001</v>
+        <v>0.994</v>
       </c>
       <c r="I14">
-        <v>0.504</v>
+        <v>0.996</v>
       </c>
       <c r="J14">
+        <v>0.01800000000000002</v>
+      </c>
+      <c r="K14">
+        <v>0.501</v>
+      </c>
+      <c r="L14">
+        <v>0.499</v>
+      </c>
+      <c r="M14">
         <v>0.503</v>
       </c>
-      <c r="K14">
-        <v>0.498</v>
-      </c>
-      <c r="L14">
-        <v>0.501</v>
-      </c>
-      <c r="M14">
-        <v>0.987</v>
-      </c>
       <c r="N14">
         <v>0.5</v>
       </c>
       <c r="O14">
-        <v>0.501</v>
-      </c>
-      <c r="P14">
-        <v>0.499</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -1130,95 +1085,42 @@
         <v>0.996</v>
       </c>
       <c r="C15">
-        <v>0.998</v>
+        <v>0.995</v>
       </c>
       <c r="D15">
-        <v>0.5</v>
+        <v>0.504</v>
       </c>
       <c r="E15">
         <v>0.994</v>
       </c>
       <c r="F15">
+        <v>0.998</v>
+      </c>
+      <c r="G15">
         <v>0.994</v>
       </c>
-      <c r="G15">
-        <v>0.508</v>
-      </c>
       <c r="H15">
-        <v>0.988</v>
+        <v>0.992</v>
       </c>
       <c r="I15">
-        <v>0.989</v>
+        <v>0.504</v>
       </c>
       <c r="J15">
-        <v>0.006000000000000005</v>
+        <v>0.501</v>
       </c>
       <c r="K15">
-        <v>0.5</v>
+        <v>0.994</v>
       </c>
       <c r="L15">
-        <v>0.499</v>
+        <v>0.505</v>
       </c>
       <c r="M15">
-        <v>0.01600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="N15">
-        <v>0.499</v>
+        <v>0.5</v>
       </c>
       <c r="O15">
-        <v>0.5</v>
-      </c>
-      <c r="P15">
-        <v>0.502</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="A16" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16">
-        <v>0.985</v>
-      </c>
-      <c r="C16">
-        <v>0.994</v>
-      </c>
-      <c r="D16">
-        <v>0.498</v>
-      </c>
-      <c r="E16">
-        <v>0.996</v>
-      </c>
-      <c r="F16">
-        <v>0.986</v>
-      </c>
-      <c r="G16">
-        <v>0.996</v>
-      </c>
-      <c r="H16">
-        <v>0.99</v>
-      </c>
-      <c r="I16">
-        <v>0.502</v>
-      </c>
-      <c r="J16">
-        <v>0.5</v>
-      </c>
-      <c r="K16">
-        <v>0.985</v>
-      </c>
-      <c r="L16">
-        <v>0.505</v>
-      </c>
-      <c r="M16">
-        <v>0.497</v>
-      </c>
-      <c r="N16">
-        <v>0.501</v>
-      </c>
-      <c r="O16">
-        <v>0.498</v>
-      </c>
-      <c r="P16">
         <v>0.5</v>
       </c>
     </row>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/matrix_scores.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/matrix_scores.xlsx
@@ -14,18 +14,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="4">
   <si>
-    <t>PPO_859</t>
+    <t>PPO_2001</t>
   </si>
   <si>
-    <t>PPO_926</t>
+    <t>PPO_2003</t>
   </si>
   <si>
-    <t>PPO_1004</t>
-  </si>
-  <si>
-    <t>PPO_1005</t>
+    <t>PPO_2004</t>
   </si>
   <si>
     <t>model</t>
@@ -386,12 +383,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -402,11 +399,8 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -414,63 +408,37 @@
         <v>0.5</v>
       </c>
       <c r="C2">
-        <v>0.014</v>
+        <v>0.008</v>
       </c>
       <c r="D2">
-        <v>0.251</v>
-      </c>
-      <c r="E2">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.986</v>
+        <v>0.992</v>
       </c>
       <c r="C3">
         <v>0.5</v>
       </c>
       <c r="D3">
-        <v>0.494</v>
-      </c>
-      <c r="E3">
-        <v>0.985</v>
+        <v>0.008</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0.749</v>
+        <v>0.992</v>
       </c>
       <c r="C4">
-        <v>0.506</v>
+        <v>0.992</v>
       </c>
       <c r="D4">
-        <v>0.5</v>
-      </c>
-      <c r="E4">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>0.996</v>
-      </c>
-      <c r="C5">
-        <v>0.01500000000000001</v>
-      </c>
-      <c r="D5">
-        <v>0.5</v>
-      </c>
-      <c r="E5">
         <v>0.5</v>
       </c>
     </row>
